--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$20:$Q$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$28:$Q$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,15 +30,19 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E5F"/>
-      <sz val="14"/>
+      <sz val="15"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="0041505E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -75,22 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,6 +95,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F3F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,20 +139,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -157,22 +167,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -569,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -583,7 +593,7 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
@@ -594,2929 +604,3165 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>権限設定 受入条件表 ─ マイルストーンごとに「どこまで実装できれば合格か」</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>下の表の「合否」に OK / NG を入れると、マイルストーンの到達状況が自動で出ます。M1→M8 が実装順です。</t>
+          <t>権限設定 受入条件表 ─ どこまで実装できれば合格か</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MVP必須＝揃わないと機能として成立しない／品質必須＝運用に耐えるために要る／推奨＝あると良い／次段階＝P1では実装せず実測を記録するだけ。M7は動作テストで検出できない境界設計＝実装物のレビューで確認する。</t>
-        </is>
-      </c>
+          <t>■ この表の位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>層</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>文書</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>何を決めるか</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>判断の主体</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1. 意図</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>仕様書 20260803_05</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>なぜそう作るか。守るべき境界（§7）。MVPとして何が揃えば価値が出るか</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>PdM</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2. 合格ライン</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>本表</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>意図を満たしたと言える定量条件。実装レベルとマイルストーン</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>PdM＋エンジニア</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3. 挙動</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>検証プラン 20260803_07</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>その条件を実際の画面・データでどう確かめるか</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>検証実施者</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>設計意図（なぜそう作るか）は仕様書にある。本表はそれを「この数値を満たせば実装完了」に翻訳する場。実際に動くかは検証プランで確かめる。</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>■ 実装レベルの定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MVP必須</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>揃わないと機能として成立しない。境界設計（K）もここに含む ── 動作テストでは検出できず、実装が違っても画面は動くが後から権限モデルが破綻するため</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>品質必須</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>事故防止・整合。無いと運用に出せない</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>利便性。無くてもリリースできる</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>次段階</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>P1では実装しない。実測を記録し次の優先順位（P2〜P5）を決める</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>■ マイルストーン到達状況（下の表の「合否」に OK / NG を入れると自動で更新）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>条件数</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>未判定</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>到達率</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C6" s="5">
-        <f>COUNTIF($A$21:$A$59,"M1 権限が作れる")</f>
-        <v/>
-      </c>
-      <c r="D6" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M1 権限が作れる",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E6" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M1 権限が作れる",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F6" s="5">
-        <f>C6-D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="6">
-        <f>IF(C6=0,"",D6/C6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(E6&gt;0,"未達（NG "&amp;E6&amp;"件）",IF(F6&gt;0,"進行中（残 "&amp;F6&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4">
+        <f>COUNTIF($A$29:$A$67,"M1 権限が作れる")</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M1 権限が作れる",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M1 権限が作れる",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>E17-F17-G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="12">
+        <f>IF(E17=0,"",F17/E17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="4">
+        <f>IF(G17&gt;0,"未達（NG "&amp;G17&amp;"件）",IF(H17&gt;0,"進行中（残 "&amp;H17&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C7" s="5">
-        <f>COUNTIF($A$21:$A$59,"M2 制御が効く")</f>
-        <v/>
-      </c>
-      <c r="D7" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M2 制御が効く",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E7" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M2 制御が効く",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F7" s="5">
-        <f>C7-D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>IF(C7=0,"",D7/C7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="5">
-        <f>IF(E7&gt;0,"未達（NG "&amp;E7&amp;"件）",IF(F7&gt;0,"進行中（残 "&amp;F7&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4">
+        <f>COUNTIF($A$29:$A$67,"M2 制御が効く")</f>
+        <v/>
+      </c>
+      <c r="F18" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M2 制御が効く",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M2 制御が効く",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H18" s="4">
+        <f>E18-F18-G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="12">
+        <f>IF(E18=0,"",F18/E18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="4">
+        <f>IF(G18&gt;0,"未達（NG "&amp;G18&amp;"件）",IF(H18&gt;0,"進行中（残 "&amp;H18&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C8" s="5">
-        <f>COUNTIF($A$21:$A$59,"M3 人に配れる")</f>
-        <v/>
-      </c>
-      <c r="D8" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M3 人に配れる",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E8" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M3 人に配れる",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F8" s="5">
-        <f>C8-D8-E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>IF(C8=0,"",D8/C8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="5">
-        <f>IF(E8&gt;0,"未達（NG "&amp;E8&amp;"件）",IF(F8&gt;0,"進行中（残 "&amp;F8&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4">
+        <f>COUNTIF($A$29:$A$67,"M3 人に配れる")</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M3 人に配れる",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M3 人に配れる",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>E19-F19-G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="12">
+        <f>IF(E19=0,"",F19/E19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>IF(G19&gt;0,"未達（NG "&amp;G19&amp;"件）",IF(H19&gt;0,"進行中（残 "&amp;H19&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C9" s="5">
-        <f>COUNTIF($A$21:$A$59,"M4 既存顧客を壊さない")</f>
-        <v/>
-      </c>
-      <c r="D9" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M4 既存顧客を壊さない",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E9" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M4 既存顧客を壊さない",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F9" s="5">
-        <f>C9-D9-E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>IF(C9=0,"",D9/C9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(E9&gt;0,"未達（NG "&amp;E9&amp;"件）",IF(F9&gt;0,"進行中（残 "&amp;F9&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4">
+        <f>COUNTIF($A$29:$A$67,"M4 既存顧客を壊さない")</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M4 既存顧客を壊さない",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M4 既存顧客を壊さない",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>E20-F20-G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="12">
+        <f>IF(E20=0,"",F20/E20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>IF(G20&gt;0,"未達（NG "&amp;G20&amp;"件）",IF(H20&gt;0,"進行中（残 "&amp;H20&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C10" s="5">
-        <f>COUNTIF($A$21:$A$59,"M5 事故らない")</f>
-        <v/>
-      </c>
-      <c r="D10" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M5 事故らない",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E10" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M5 事故らない",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F10" s="5">
-        <f>C10-D10-E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>IF(C10=0,"",D10/C10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="5">
-        <f>IF(E10&gt;0,"未達（NG "&amp;E10&amp;"件）",IF(F10&gt;0,"進行中（残 "&amp;F10&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4">
+        <f>COUNTIF($A$29:$A$67,"M5 事故らない")</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M5 事故らない",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M5 事故らない",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>E21-F21-G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="12">
+        <f>IF(E21=0,"",F21/E21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>IF(G21&gt;0,"未達（NG "&amp;G21&amp;"件）",IF(H21&gt;0,"進行中（残 "&amp;H21&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C11" s="5">
-        <f>COUNTIF($A$21:$A$59,"M6 運用できる")</f>
-        <v/>
-      </c>
-      <c r="D11" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M6 運用できる",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E11" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M6 運用できる",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F11" s="5">
-        <f>C11-D11-E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>IF(C11=0,"",D11/C11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="5">
-        <f>IF(E11&gt;0,"未達（NG "&amp;E11&amp;"件）",IF(F11&gt;0,"進行中（残 "&amp;F11&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4">
+        <f>COUNTIF($A$29:$A$67,"M6 運用できる")</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M6 運用できる",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M6 運用できる",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>E22-F22-G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="12">
+        <f>IF(E22=0,"",F22/E22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>IF(G22&gt;0,"未達（NG "&amp;G22&amp;"件）",IF(H22&gt;0,"進行中（残 "&amp;H22&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C12" s="5">
-        <f>COUNTIF($A$21:$A$59,"M7 境界設計が守られている")</f>
-        <v/>
-      </c>
-      <c r="D12" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M7 境界設計が守られている",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M7 境界設計が守られている",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F12" s="5">
-        <f>C12-D12-E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="6">
-        <f>IF(C12=0,"",D12/C12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="5">
-        <f>IF(E12&gt;0,"未達（NG "&amp;E12&amp;"件）",IF(F12&gt;0,"進行中（残 "&amp;F12&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4">
+        <f>COUNTIF($A$29:$A$67,"M7 境界設計が守られている")</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M7 境界設計が守られている",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M7 境界設計が守られている",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>E23-F23-G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="12">
+        <f>IF(E23=0,"",F23/E23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="4">
+        <f>IF(G23&gt;0,"未達（NG "&amp;G23&amp;"件）",IF(H23&gt;0,"進行中（残 "&amp;H23&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>M8 顧客価値に到達</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
-      <c r="C13" s="5">
-        <f>COUNTIF($A$21:$A$59,"M8 顧客価値に到達")</f>
-        <v/>
-      </c>
-      <c r="D13" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M8 顧客価値に到達",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E13" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M8 顧客価値に到達",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F13" s="5">
-        <f>C13-D13-E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>IF(C13=0,"",D13/C13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(E13&gt;0,"未達（NG "&amp;E13&amp;"件）",IF(F13&gt;0,"進行中（残 "&amp;F13&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4">
+        <f>COUNTIF($A$29:$A$67,"M8 顧客価値に到達")</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M8 顧客価値に到達",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M8 顧客価値に到達",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>E24-F24-G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="12">
+        <f>IF(E24=0,"",F24/E24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>IF(G24&gt;0,"未達（NG "&amp;G24&amp;"件）",IF(H24&gt;0,"進行中（残 "&amp;H24&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C14" s="5">
-        <f>COUNTIF($A$21:$A$59,"M9 次段階（P1対象外）")</f>
-        <v/>
-      </c>
-      <c r="D14" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M9 次段階（P1対象外）",$N$21:$N$59,"OK")</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>COUNTIFS($A$21:$A$59,"M9 次段階（P1対象外）",$N$21:$N$59,"NG")</f>
-        <v/>
-      </c>
-      <c r="F14" s="5">
-        <f>C14-D14-E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="6">
-        <f>IF(C14=0,"",D14/C14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="5">
-        <f>IF(E14&gt;0,"未達（NG "&amp;E14&amp;"件）",IF(F14&gt;0,"進行中（残 "&amp;F14&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4">
+        <f>COUNTIF($A$29:$A$67,"M9 次段階（P1対象外）")</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M9 次段階（P1対象外）",$N$29:$N$67,"OK")</f>
+        <v/>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIFS($A$29:$A$67,"M9 次段階（P1対象外）",$N$29:$N$67,"NG")</f>
+        <v/>
+      </c>
+      <c r="H25" s="4">
+        <f>E25-F25-G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="12">
+        <f>IF(E25=0,"",F25/E25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="4">
+        <f>IF(G25&gt;0,"未達（NG "&amp;G25&amp;"件）",IF(H25&gt;0,"進行中（残 "&amp;H25&amp;"件）","完了"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>総合判定</t>
         </is>
       </c>
-      <c r="B15" s="8">
-        <f>IF(COUNTIFS($E$21:$E$59,"MVP必須",$N$21:$N$59,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$21:$E$59,"MVP必須",$N$21:$N$59,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$21:$E$59,"MVP必須")-COUNTIFS($E$21:$E$59,"MVP必須",$N$21:$N$59,"OK")-COUNTIFS($E$21:$E$59,"MVP必須",$N$21:$N$59,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$21:$E$59,"MVP必須")-COUNTIFS($E$21:$E$59,"MVP必須",$N$21:$N$59,"OK")-COUNTIFS($E$21:$E$59,"MVP必須",$N$21:$N$59,"NG"))&amp;"件）",IF(COUNTIFS($E$21:$E$59,"品質必須",$N$21:$N$59,"NG")&gt;0,"MVP到達。品質必須にNGあり ── 運用でカバーできるかPdMが判断","MVP到達・品質必須も充足 ── リリース可")))</f>
-        <v/>
-      </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="B26" s="14">
+        <f>IF(COUNTIFS($E$29:$E$67,"MVP必須",$N$29:$N$67,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$29:$E$67,"MVP必須",$N$29:$N$67,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$29:$E$67,"MVP必須")-COUNTIFS($E$29:$E$67,"MVP必須",$N$29:$N$67,"OK")-COUNTIFS($E$29:$E$67,"MVP必須",$N$29:$N$67,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$29:$E$67,"MVP必須")-COUNTIFS($E$29:$E$67,"MVP必須",$N$29:$N$67,"OK")-COUNTIFS($E$29:$E$67,"MVP必須",$N$29:$N$67,"NG"))&amp;"件）",IF(COUNTIFS($E$29:$E$67,"品質必須",$N$29:$N$67,"NG")&gt;0,"MVP到達。品質必須にNGあり ── 運用でカバーできるかPdMが判断","MVP到達・品質必須も充足 ── リリース可")))</f>
+        <v/>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>マイルストーンの完了条件</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>設計ポイント</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>条件ID</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>実装レベル</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>何を実装するか</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>合格ライン（この数値を満たせば実装完了）</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H28" s="15" t="inlineStr">
         <is>
           <t>実装できていないと起きること</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>実装箇所</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>確認する画面</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K28" s="15" t="inlineStr">
         <is>
           <t>対応検証ID</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L28" s="15" t="inlineStr">
         <is>
           <t>仕様書の根拠</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M28" s="15" t="inlineStr">
         <is>
           <t>エビデンス</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr">
+      <c r="N28" s="15" t="inlineStr">
         <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="O20" s="9" t="inlineStr">
+      <c r="O28" s="15" t="inlineStr">
         <is>
           <t>実測値</t>
         </is>
       </c>
-      <c r="P20" s="9" t="inlineStr">
+      <c r="P28" s="15" t="inlineStr">
         <is>
           <t>判定者</t>
         </is>
       </c>
-      <c r="Q20" s="9" t="inlineStr">
+      <c r="Q28" s="15" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>会社／店舗の区分で、設定対象の画面を出し分ける</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr">
         <is>
           <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリが設定対象に出る</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>会社用・店舗用の権限を別々に作れない。機能の前提が崩れる</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>権限編集（区分の選択→権限内容）</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J29" s="18" t="inlineStr">
         <is>
           <t>権限編集（区分の切替）</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
+      <c r="K29" s="18" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L29" s="18" t="inlineStr">
         <is>
           <t>§3.3 カテゴリ構成</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
+      <c r="M29" s="18" t="inlineStr">
         <is>
           <t>T-03.png</t>
         </is>
       </c>
-      <c r="N21" s="14" t="inlineStr"/>
-      <c r="O21" s="14" t="inlineStr"/>
-      <c r="P21" s="14" t="inlineStr"/>
-      <c r="Q21" s="14" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr"/>
-      <c r="B22" s="11" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="N29" s="20" t="inlineStr"/>
+      <c r="O29" s="20" t="inlineStr"/>
+      <c r="P29" s="20" t="inlineStr"/>
+      <c r="Q29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr"/>
+      <c r="B30" s="17" t="inlineStr"/>
+      <c r="C30" s="17" t="inlineStr"/>
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>区分に該当しない画面を設定対象に出さない</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>会社で店舗専用6が出ない、店舗で会社専用4が出ない</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>会社の権限に店舗専用画面が出るなど、設定時に誤った選択肢を選べてしまう</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>権限編集（カテゴリの ctx 判定）</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr">
         <is>
           <t>権限編集（権限内容）</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="K30" s="18" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L30" s="18" t="inlineStr">
         <is>
           <t>§3.3</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M30" s="18" t="inlineStr">
         <is>
           <t>T-03.png</t>
         </is>
       </c>
-      <c r="N22" s="14" t="inlineStr"/>
-      <c r="O22" s="14" t="inlineStr"/>
-      <c r="P22" s="14" t="inlineStr"/>
-      <c r="Q22" s="14" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr"/>
-      <c r="B23" s="11" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="N30" s="20" t="inlineStr"/>
+      <c r="O30" s="20" t="inlineStr"/>
+      <c r="P30" s="20" t="inlineStr"/>
+      <c r="Q30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr"/>
+      <c r="B31" s="17" t="inlineStr"/>
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>権限の作成・保存・再表示が往復して壊れない</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>保存→再表示で欠落・反転=0件</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>設定した権限が保存されない。機能として成立しない</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>権限編集／roles・role_permissions</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J31" s="18" t="inlineStr">
         <is>
           <t>権限編集（保存→再表示）</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
+      <c r="K31" s="18" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L31" s="18" t="inlineStr">
         <is>
           <t>§5.2 権限編集</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="M31" s="18" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="N23" s="14" t="inlineStr"/>
-      <c r="O23" s="14" t="inlineStr"/>
-      <c r="P23" s="14" t="inlineStr"/>
-      <c r="Q23" s="14" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr"/>
-      <c r="B24" s="11" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr"/>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="N31" s="20" t="inlineStr"/>
+      <c r="O31" s="20" t="inlineStr"/>
+      <c r="P31" s="20" t="inlineStr"/>
+      <c r="Q31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr"/>
+      <c r="B32" s="17" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr"/>
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>AC-08</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E32" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>雛形（ベース）から差分で作れる。移植プリセットを候補に出す</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>ベース選択に4種（オーナー相当/本部管理/店長/従業員）＋プレーンが出る。エリア長は含まれない</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>27画面をゼロから設定することになり、実運用が回らない</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>権限編集①ベース選択</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>権限編集（＋権限を新規作成）</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
+      <c r="K32" s="18" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>§5.2 ベース候補</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="inlineStr">
+      <c r="L32" s="18" t="inlineStr">
+        <is>
+          <t>§5.2 / §7-H'</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>T-01.png</t>
         </is>
       </c>
-      <c r="N24" s="14" t="inlineStr"/>
-      <c r="O24" s="14" t="inlineStr"/>
-      <c r="P24" s="14" t="inlineStr"/>
-      <c r="Q24" s="14" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr"/>
-      <c r="B25" s="11" t="inlineStr"/>
-      <c r="C25" s="11" t="inlineStr"/>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="N32" s="20" t="inlineStr"/>
+      <c r="O32" s="20" t="inlineStr"/>
+      <c r="P32" s="20" t="inlineStr"/>
+      <c r="Q32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr"/>
+      <c r="B33" s="17" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr"/>
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>AC-09</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>ゼロから作る場合は全項目オフで始まる</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>プレーン選択時に許可=0件</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>意図せず開いた状態の権限ができる</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>権限編集（プレーン）</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J33" s="18" t="inlineStr">
         <is>
           <t>権限編集（プレーン選択時）</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="K33" s="18" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L33" s="18" t="inlineStr">
         <is>
           <t>§5.2</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr">
+      <c r="M33" s="18" t="inlineStr">
         <is>
           <t>T-02.png</t>
         </is>
       </c>
-      <c r="N25" s="14" t="inlineStr"/>
-      <c r="O25" s="14" t="inlineStr"/>
-      <c r="P25" s="14" t="inlineStr"/>
-      <c r="Q25" s="14" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr"/>
-      <c r="B26" s="11" t="inlineStr"/>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="N33" s="20" t="inlineStr"/>
+      <c r="O33" s="20" t="inlineStr"/>
+      <c r="P33" s="20" t="inlineStr"/>
+      <c r="Q33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr"/>
+      <c r="B34" s="17" t="inlineStr"/>
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>AC-12</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>権限が未定義の画面は既定で塞ぐ（fail-closed）</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>新規追加画面が全ロールで なし</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>今後追加される画面が全権限に開いた状態で出る</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>判定層の既定値</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J34" s="18" t="inlineStr">
         <is>
           <t>権限編集</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
+      <c r="K34" s="18" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L34" s="18" t="inlineStr">
         <is>
           <t>§9 fail-closed</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M34" s="18" t="inlineStr">
         <is>
           <t>T-02.png</t>
         </is>
       </c>
-      <c r="N26" s="14" t="inlineStr"/>
-      <c r="O26" s="14" t="inlineStr"/>
-      <c r="P26" s="14" t="inlineStr"/>
-      <c r="Q26" s="14" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr"/>
-      <c r="B27" s="11" t="inlineStr"/>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="N34" s="20" t="inlineStr"/>
+      <c r="O34" s="20" t="inlineStr"/>
+      <c r="P34" s="20" t="inlineStr"/>
+      <c r="Q34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr"/>
+      <c r="B35" s="17" t="inlineStr"/>
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F35" s="18" t="inlineStr">
         <is>
           <t>導入時に推奨権限をまとめて登録できる（下書きの保存・破棄を含む）</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>権限テンプレートが適用でき権限一覧に登録される。下書きの一時保存で復元、破棄で初期化できる</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>導入時に権限を用意できず、導入作業そのものが始められない</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>権限テンプレート画面</t>
         </is>
       </c>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="J35" s="18" t="inlineStr">
         <is>
           <t>権限テンプレート</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr">
+      <c r="K35" s="18" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L35" s="18" t="inlineStr">
         <is>
           <t>§5.6 F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr">
+      <c r="M35" s="18" t="inlineStr">
         <is>
           <t>T-04.png</t>
         </is>
       </c>
-      <c r="N27" s="14" t="inlineStr"/>
-      <c r="O27" s="14" t="inlineStr"/>
-      <c r="P27" s="14" t="inlineStr"/>
-      <c r="Q27" s="14" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="N35" s="20" t="inlineStr"/>
+      <c r="O35" s="20" t="inlineStr"/>
+      <c r="P35" s="20" t="inlineStr"/>
+      <c r="Q35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>許可した画面が開ける</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>見えるべき画面=100%開ける</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>必要な画面が開けず現場の業務が止まる</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>各画面の表示判定</t>
         </is>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J36" s="18" t="inlineStr">
         <is>
           <t>全画面（各権限でログイン）</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="K36" s="18" t="inlineStr">
         <is>
           <t>T-09〜T-14</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L36" s="18" t="inlineStr">
         <is>
           <t>§3.1 ①画面</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr">
+      <c r="M36" s="18" t="inlineStr">
         <is>
           <t>T-09.png</t>
         </is>
       </c>
-      <c r="N28" s="14" t="inlineStr"/>
-      <c r="O28" s="14" t="inlineStr"/>
-      <c r="P28" s="14" t="inlineStr"/>
-      <c r="Q28" s="14" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr"/>
-      <c r="B29" s="11" t="inlineStr"/>
-      <c r="C29" s="11" t="inlineStr"/>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="N36" s="20" t="inlineStr"/>
+      <c r="O36" s="20" t="inlineStr"/>
+      <c r="P36" s="20" t="inlineStr"/>
+      <c r="Q36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr"/>
+      <c r="B37" s="17" t="inlineStr"/>
+      <c r="C37" s="17" t="inlineStr"/>
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>許可していない画面が開けない。メニュー非表示だけでなく直URLも塞ぐ</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>メニュー非表示かつ直URLでも開けない=100%</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>見せてはいけない画面が見える＝情報漏洩</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>コントローラの認可（メニュー生成だけでは不可）</t>
         </is>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>全画面（直URLを含む）</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
+      <c r="K37" s="18" t="inlineStr">
         <is>
           <t>T-09〜T-14</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="L37" s="18" t="inlineStr">
         <is>
           <t>§9 誤って通す</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr">
+      <c r="M37" s="18" t="inlineStr">
         <is>
           <t>T-09.png</t>
         </is>
       </c>
-      <c r="N29" s="14" t="inlineStr"/>
-      <c r="O29" s="14" t="inlineStr"/>
-      <c r="P29" s="14" t="inlineStr"/>
-      <c r="Q29" s="14" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr"/>
-      <c r="B30" s="11" t="inlineStr"/>
-      <c r="C30" s="11" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="N37" s="20" t="inlineStr"/>
+      <c r="O37" s="20" t="inlineStr"/>
+      <c r="P37" s="20" t="inlineStr"/>
+      <c r="Q37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr"/>
+      <c r="B38" s="17" t="inlineStr"/>
+      <c r="C38" s="17" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
         <is>
           <t>権限を最小にしてもログインでき、ランディングに着地する</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>全項目オフのロールでログインでき着地画面が出る</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>権限を絞ると使えなくなる＝絞る運用そのものができない</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>ダッシュボード＝閲覧固定</t>
         </is>
       </c>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>ダッシュボード</t>
         </is>
       </c>
-      <c r="K30" s="12" t="inlineStr">
+      <c r="K38" s="18" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L38" s="18" t="inlineStr">
         <is>
           <t>§9 誤って塞ぐ</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr">
+      <c r="M38" s="18" t="inlineStr">
         <is>
           <t>T-14.png</t>
         </is>
       </c>
-      <c r="N30" s="14" t="inlineStr"/>
-      <c r="O30" s="14" t="inlineStr"/>
-      <c r="P30" s="14" t="inlineStr"/>
-      <c r="Q30" s="14" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr"/>
-      <c r="B31" s="11" t="inlineStr"/>
-      <c r="C31" s="11" t="inlineStr"/>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="N38" s="20" t="inlineStr"/>
+      <c r="O38" s="20" t="inlineStr"/>
+      <c r="P38" s="20" t="inlineStr"/>
+      <c r="Q38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr"/>
+      <c r="B39" s="17" t="inlineStr"/>
+      <c r="C39" s="17" t="inlineStr"/>
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
         <is>
           <t>設定変更が反映される（即時または再ログイン）</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>即時または再ログインで反映（無反映はNG）</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>権限を変更しても効かない</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>権限のキャッシュ・セッション</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J39" s="18" t="inlineStr">
         <is>
           <t>全画面（変更後に遷移）</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K39" s="18" t="inlineStr">
         <is>
           <t>T-08</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L39" s="18" t="inlineStr">
         <is>
           <t>§8-6</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
+      <c r="M39" s="18" t="inlineStr">
         <is>
           <t>T-08.png</t>
         </is>
       </c>
-      <c r="N31" s="14" t="inlineStr"/>
-      <c r="O31" s="14" t="inlineStr"/>
-      <c r="P31" s="14" t="inlineStr"/>
-      <c r="Q31" s="14" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="N39" s="20" t="inlineStr"/>
+      <c r="O39" s="20" t="inlineStr"/>
+      <c r="P39" s="20" t="inlineStr"/>
+      <c r="Q39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F40" s="18" t="inlineStr">
         <is>
           <t>既存の全管理者に権限が割り当たる（移行漏れ0）</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>ロール未割当=0名</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>権限が付いていない管理者はログインしても何も見えない</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>移行処理</t>
         </is>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J40" s="18" t="inlineStr">
         <is>
           <t>ユーザー割当</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="K40" s="18" t="inlineStr">
         <is>
           <t>T-18 T-21</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L40" s="18" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr">
+      <c r="M40" s="18" t="inlineStr">
         <is>
           <t>ユーザー割当一覧のスクショ（未割当0名）</t>
         </is>
       </c>
-      <c r="N32" s="14" t="inlineStr"/>
-      <c r="O32" s="14" t="inlineStr"/>
-      <c r="P32" s="14" t="inlineStr"/>
-      <c r="Q32" s="14" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr"/>
-      <c r="B33" s="11" t="inlineStr"/>
-      <c r="C33" s="11" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="N40" s="20" t="inlineStr"/>
+      <c r="O40" s="20" t="inlineStr"/>
+      <c r="P40" s="20" t="inlineStr"/>
+      <c r="Q40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr"/>
+      <c r="B41" s="17" t="inlineStr"/>
+      <c r="C41" s="17" t="inlineStr"/>
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>AC-14</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F41" s="18" t="inlineStr">
         <is>
           <t>1人1ロール。付け替えで前の権限が確実に外れる</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>割当編集で同時に選べる権限=1つ。付け替えで前の権限の画面=0件</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>前の権限が残り、想定外の画面が見えたままになる</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>割当編集／user_roles</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J41" s="18" t="inlineStr">
         <is>
           <t>割当編集</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="K41" s="18" t="inlineStr">
         <is>
           <t>S-05 T-15</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>§3.5 1人1ロール</t>
-        </is>
-      </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="L41" s="18" t="inlineStr">
+        <is>
+          <t>§3.5 / §7-H</t>
+        </is>
+      </c>
+      <c r="M41" s="18" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="N33" s="14" t="inlineStr"/>
-      <c r="O33" s="14" t="inlineStr"/>
-      <c r="P33" s="14" t="inlineStr"/>
-      <c r="Q33" s="14" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr"/>
-      <c r="B34" s="11" t="inlineStr"/>
-      <c r="C34" s="11" t="inlineStr"/>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="N41" s="20" t="inlineStr"/>
+      <c r="O41" s="20" t="inlineStr"/>
+      <c r="P41" s="20" t="inlineStr"/>
+      <c r="Q41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr"/>
+      <c r="B42" s="17" t="inlineStr"/>
+      <c r="C42" s="17" t="inlineStr"/>
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F42" s="18" t="inlineStr">
         <is>
           <t>付け替えで既存権限が置き換わることを事前に明示する</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>登録済み/置換予告が該当行に表示=100%</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>付け替えで意図せず権限を剥奪してしまう</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>割当編集／一括割当のUI</t>
         </is>
       </c>
-      <c r="J34" s="12" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t>割当編集／一括割当</t>
         </is>
       </c>
-      <c r="K34" s="12" t="inlineStr">
+      <c r="K42" s="18" t="inlineStr">
         <is>
           <t>T-15 T-16</t>
         </is>
       </c>
-      <c r="L34" s="12" t="inlineStr">
+      <c r="L42" s="18" t="inlineStr">
         <is>
           <t>§5.4 事故防止3点</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr">
+      <c r="M42" s="18" t="inlineStr">
         <is>
           <t>T-15.png</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr"/>
-      <c r="O34" s="14" t="inlineStr"/>
-      <c r="P34" s="14" t="inlineStr"/>
-      <c r="Q34" s="14" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr"/>
-      <c r="B35" s="11" t="inlineStr"/>
-      <c r="C35" s="11" t="inlineStr"/>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="N42" s="20" t="inlineStr"/>
+      <c r="O42" s="20" t="inlineStr"/>
+      <c r="P42" s="20" t="inlineStr"/>
+      <c r="Q42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr"/>
+      <c r="B43" s="17" t="inlineStr"/>
+      <c r="C43" s="17" t="inlineStr"/>
+      <c r="D43" s="18" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F43" s="18" t="inlineStr">
         <is>
           <t>担当店舗を複数紐付けられる（人ごとに異なる範囲）</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>店長ベースで作った権限に2店舗を紐付けて保存できる</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H43" s="18" t="inlineStr">
         <is>
           <t>エリアマネージャーなど複数店舗を担当する権限が作れない</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>割当編集（store_ids）</t>
         </is>
       </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="J43" s="18" t="inlineStr">
         <is>
           <t>割当編集（対象店舗）</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr">
+      <c r="K43" s="18" t="inlineStr">
         <is>
           <t>S-05 T-11</t>
         </is>
       </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>§3.1 ④</t>
-        </is>
-      </c>
-      <c r="M35" s="12" t="inlineStr">
+      <c r="L43" s="18" t="inlineStr">
+        <is>
+          <t>§3.1④ / §7-B</t>
+        </is>
+      </c>
+      <c r="M43" s="18" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="N35" s="14" t="inlineStr"/>
-      <c r="O35" s="14" t="inlineStr"/>
-      <c r="P35" s="14" t="inlineStr"/>
-      <c r="Q35" s="14" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr"/>
-      <c r="B36" s="11" t="inlineStr"/>
-      <c r="C36" s="11" t="inlineStr"/>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="N43" s="20" t="inlineStr"/>
+      <c r="O43" s="20" t="inlineStr"/>
+      <c r="P43" s="20" t="inlineStr"/>
+      <c r="Q43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr"/>
+      <c r="B44" s="17" t="inlineStr"/>
+      <c r="C44" s="17" t="inlineStr"/>
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E44" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F44" s="18" t="inlineStr">
         <is>
           <t>店舗ロールで担当店舗が未設定の割当を検知する</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>エラーまたは警告が出る</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H44" s="18" t="inlineStr">
         <is>
           <t>担当店舗が未設定のまま割り当てられ、何も見えない人ができる</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>割当編集のバリデーション</t>
         </is>
       </c>
-      <c r="J36" s="12" t="inlineStr">
+      <c r="J44" s="18" t="inlineStr">
         <is>
           <t>割当編集</t>
         </is>
       </c>
-      <c r="K36" s="12" t="inlineStr">
+      <c r="K44" s="18" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="L36" s="12" t="inlineStr">
+      <c r="L44" s="18" t="inlineStr">
         <is>
           <t>§5.4</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr">
+      <c r="M44" s="18" t="inlineStr">
         <is>
           <t>T-18.png</t>
         </is>
       </c>
-      <c r="N36" s="14" t="inlineStr"/>
-      <c r="O36" s="14" t="inlineStr"/>
-      <c r="P36" s="14" t="inlineStr"/>
-      <c r="Q36" s="14" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="N44" s="20" t="inlineStr"/>
+      <c r="O44" s="20" t="inlineStr"/>
+      <c r="P44" s="20" t="inlineStr"/>
+      <c r="Q44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F45" s="18" t="inlineStr">
         <is>
           <t>master と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G45" s="18" t="inlineStr">
         <is>
           <t>適用前後で見える画面の増減=0</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H45" s="18" t="inlineStr">
         <is>
           <t>既存の master 権限で見える画面が増減する。増えれば情報漏洩、減れば業務停止</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="J45" s="18" t="inlineStr">
         <is>
           <t>全画面（master でログイン）</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
+      <c r="K45" s="18" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L45" s="18" t="inlineStr">
         <is>
           <t>§4 段階導入</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr">
+      <c r="M45" s="18" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N37" s="14" t="inlineStr"/>
-      <c r="O37" s="14" t="inlineStr"/>
-      <c r="P37" s="14" t="inlineStr"/>
-      <c r="Q37" s="14" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr"/>
-      <c r="B38" s="11" t="inlineStr"/>
-      <c r="C38" s="11" t="inlineStr"/>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="N45" s="20" t="inlineStr"/>
+      <c r="O45" s="20" t="inlineStr"/>
+      <c r="P45" s="20" t="inlineStr"/>
+      <c r="Q45" s="20" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr"/>
+      <c r="B46" s="17" t="inlineStr"/>
+      <c r="C46" s="17" t="inlineStr"/>
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E46" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F46" s="18" t="inlineStr">
         <is>
           <t>manager と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G46" s="18" t="inlineStr">
         <is>
           <t>増減=0</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H46" s="18" t="inlineStr">
         <is>
           <t>既存の manager 権限で見える画面が増減する</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J46" s="18" t="inlineStr">
         <is>
           <t>全画面（manager でログイン）</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr">
+      <c r="K46" s="18" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L46" s="18" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr">
+      <c r="M46" s="18" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N38" s="14" t="inlineStr"/>
-      <c r="O38" s="14" t="inlineStr"/>
-      <c r="P38" s="14" t="inlineStr"/>
-      <c r="Q38" s="14" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr"/>
-      <c r="B39" s="11" t="inlineStr"/>
-      <c r="C39" s="11" t="inlineStr"/>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="N46" s="20" t="inlineStr"/>
+      <c r="O46" s="20" t="inlineStr"/>
+      <c r="P46" s="20" t="inlineStr"/>
+      <c r="Q46" s="20" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr"/>
+      <c r="B47" s="17" t="inlineStr"/>
+      <c r="C47" s="17" t="inlineStr"/>
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F47" s="18" t="inlineStr">
         <is>
           <t>shop_manager と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>増減=0</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H47" s="18" t="inlineStr">
         <is>
           <t>既存の shop_manager 権限で見える画面が増減する</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="J47" s="18" t="inlineStr">
         <is>
           <t>全画面（shop_manager でログイン）</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr">
+      <c r="K47" s="18" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L39" s="12" t="inlineStr">
+      <c r="L47" s="18" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr">
+      <c r="M47" s="18" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N39" s="14" t="inlineStr"/>
-      <c r="O39" s="14" t="inlineStr"/>
-      <c r="P39" s="14" t="inlineStr"/>
-      <c r="Q39" s="14" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="N47" s="20" t="inlineStr"/>
+      <c r="O47" s="20" t="inlineStr"/>
+      <c r="P47" s="20" t="inlineStr"/>
+      <c r="Q47" s="20" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>F. 事故を防ぐ</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>AC-17</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F48" s="18" t="inlineStr">
         <is>
           <t>自分の権限から権限設定を外せない（自己ロックアウト防止）</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G48" s="18" t="inlineStr">
         <is>
           <t>権限設定を自ロールから外す操作が警告またはブロック</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H48" s="18" t="inlineStr">
         <is>
           <t>管理者が自分を締め出し、復旧に開発対応が必要になる</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>権限編集の保存時チェック</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J48" s="18" t="inlineStr">
         <is>
           <t>権限編集</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
+      <c r="K48" s="18" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L48" s="18" t="inlineStr">
         <is>
           <t>§9 自己ロックアウト</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr">
+      <c r="M48" s="18" t="inlineStr">
         <is>
           <t>T-17.png</t>
         </is>
       </c>
-      <c r="N40" s="14" t="inlineStr"/>
-      <c r="O40" s="14" t="inlineStr"/>
-      <c r="P40" s="14" t="inlineStr"/>
-      <c r="Q40" s="14" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr"/>
-      <c r="B41" s="11" t="inlineStr"/>
-      <c r="C41" s="11" t="inlineStr"/>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="N48" s="20" t="inlineStr"/>
+      <c r="O48" s="20" t="inlineStr"/>
+      <c r="P48" s="20" t="inlineStr"/>
+      <c r="Q48" s="20" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr"/>
+      <c r="B49" s="17" t="inlineStr"/>
+      <c r="C49" s="17" t="inlineStr"/>
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F49" s="18" t="inlineStr">
         <is>
           <t>一般の権限で権限設定ページを開けない</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G49" s="18" t="inlineStr">
         <is>
           <t>店舗ロールで権限設定URL=ブロック</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H49" s="18" t="inlineStr">
         <is>
           <t>一般の権限で権限設定を書き換えられる＝権限機能全体が無意味になる</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>権限設定画面の認可</t>
         </is>
       </c>
-      <c r="J41" s="12" t="inlineStr">
+      <c r="J49" s="18" t="inlineStr">
         <is>
           <t>権限設定（直URL）</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr">
+      <c r="K49" s="18" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L49" s="18" t="inlineStr">
         <is>
           <t>§9</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr">
+      <c r="M49" s="18" t="inlineStr">
         <is>
           <t>T-17.png</t>
         </is>
       </c>
-      <c r="N41" s="14" t="inlineStr"/>
-      <c r="O41" s="14" t="inlineStr"/>
-      <c r="P41" s="14" t="inlineStr"/>
-      <c r="Q41" s="14" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="N49" s="20" t="inlineStr"/>
+      <c r="O49" s="20" t="inlineStr"/>
+      <c r="P49" s="20" t="inlineStr"/>
+      <c r="Q49" s="20" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>一覧の許可数が実際の設定と一致する</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G50" s="18" t="inlineStr">
         <is>
           <t>不一致=0件（5ロールで検証）</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H50" s="18" t="inlineStr">
         <is>
           <t>一覧の表示と実際の設定がズレ、確認を誤る</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>権限一覧の集計</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J50" s="18" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr">
+      <c r="K50" s="18" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L50" s="18" t="inlineStr">
         <is>
           <t>§5.3 権限一覧</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr">
+      <c r="M50" s="18" t="inlineStr">
         <is>
           <t>T-05.png</t>
         </is>
       </c>
-      <c r="N42" s="14" t="inlineStr"/>
-      <c r="O42" s="14" t="inlineStr"/>
-      <c r="P42" s="14" t="inlineStr"/>
-      <c r="Q42" s="14" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr"/>
-      <c r="B43" s="11" t="inlineStr"/>
-      <c r="C43" s="11" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="N50" s="20" t="inlineStr"/>
+      <c r="O50" s="20" t="inlineStr"/>
+      <c r="P50" s="20" t="inlineStr"/>
+      <c r="Q50" s="20" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr"/>
+      <c r="B51" s="17" t="inlineStr"/>
+      <c r="C51" s="17" t="inlineStr"/>
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>権限編集はどの入口から入っても元の画面に戻る</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G51" s="18" t="inlineStr">
         <is>
           <t>4入口すべてで来た元に戻る（一覧/セルクリック/役割サマリ/割当編集）</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>修正のたびに元の場所へ辿り直すことになり、点検作業が重くなる</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>遷移の origin 保持</t>
         </is>
       </c>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="J51" s="18" t="inlineStr">
         <is>
           <t>権限編集（4入口）</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K51" s="18" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L51" s="18" t="inlineStr">
         <is>
           <t>§5.6 F-06〜F-09</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr">
+      <c r="M51" s="18" t="inlineStr">
         <is>
           <t>T-07.png</t>
         </is>
       </c>
-      <c r="N43" s="14" t="inlineStr"/>
-      <c r="O43" s="14" t="inlineStr"/>
-      <c r="P43" s="14" t="inlineStr"/>
-      <c r="Q43" s="14" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr"/>
-      <c r="B44" s="11" t="inlineStr"/>
-      <c r="C44" s="11" t="inlineStr"/>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="N51" s="20" t="inlineStr"/>
+      <c r="O51" s="20" t="inlineStr"/>
+      <c r="P51" s="20" t="inlineStr"/>
+      <c r="Q51" s="20" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr"/>
+      <c r="B52" s="17" t="inlineStr"/>
+      <c r="C52" s="17" t="inlineStr"/>
+      <c r="D52" s="18" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>役割サマリの割当人数が実態と一致する</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G52" s="18" t="inlineStr">
         <is>
           <t>6権限すべてで 表示N＝実保持者数（差分0）</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H52" s="18" t="inlineStr">
         <is>
           <t>割当人数の表示が実態とズレ、点検の判断を誤る</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>役割サマリの集計</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J52" s="18" t="inlineStr">
         <is>
           <t>役割サマリ</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="K52" s="18" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L52" s="18" t="inlineStr">
         <is>
           <t>§5.4 役割サマリ</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr">
+      <c r="M52" s="18" t="inlineStr">
         <is>
           <t>T-06.png</t>
         </is>
       </c>
-      <c r="N44" s="14" t="inlineStr"/>
-      <c r="O44" s="14" t="inlineStr"/>
-      <c r="P44" s="14" t="inlineStr"/>
-      <c r="Q44" s="14" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr"/>
-      <c r="B45" s="11" t="inlineStr"/>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="N52" s="20" t="inlineStr"/>
+      <c r="O52" s="20" t="inlineStr"/>
+      <c r="P52" s="20" t="inlineStr"/>
+      <c r="Q52" s="20" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr"/>
+      <c r="B53" s="17" t="inlineStr"/>
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>H. 指標とオーナー</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D53" s="18" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E53" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F53" s="18" t="inlineStr">
         <is>
           <t>指標をまとめて設定でき、他の権限に再利用できる</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>テンプレ適用の結果が定義と一致。保存した組み合わせを他権限で読込できる</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H53" s="18" t="inlineStr">
         <is>
           <t>権限ごとに指標を作り直すことになり運用負荷が高い</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J53" s="18" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K53" s="18" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L53" s="18" t="inlineStr">
         <is>
           <t>§5.5</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr">
+      <c r="M53" s="18" t="inlineStr">
         <is>
           <t>T-20.png</t>
         </is>
       </c>
-      <c r="N45" s="14" t="inlineStr"/>
-      <c r="O45" s="14" t="inlineStr"/>
-      <c r="P45" s="14" t="inlineStr"/>
-      <c r="Q45" s="14" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr"/>
-      <c r="B46" s="11" t="inlineStr"/>
-      <c r="C46" s="11" t="inlineStr"/>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="N53" s="20" t="inlineStr"/>
+      <c r="O53" s="20" t="inlineStr"/>
+      <c r="P53" s="20" t="inlineStr"/>
+      <c r="Q53" s="20" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr"/>
+      <c r="B54" s="17" t="inlineStr"/>
+      <c r="C54" s="17" t="inlineStr"/>
+      <c r="D54" s="18" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
         <is>
           <t>オーナー専用機能が読取専用・オーナー限定である</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G54" s="18" t="inlineStr">
         <is>
           <t>指標管理に編集UIが出ない。付与先指定はオーナーのみ実行可</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H54" s="18" t="inlineStr">
         <is>
           <t>全権の設定が誤って変更される</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>オーナー操作</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J54" s="18" t="inlineStr">
         <is>
           <t>オーナー操作</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K54" s="18" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="L54" s="18" t="inlineStr">
         <is>
           <t>§5.3 オーナー操作</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr">
+      <c r="M54" s="18" t="inlineStr">
         <is>
           <t>T-20.png</t>
         </is>
       </c>
-      <c r="N46" s="14" t="inlineStr"/>
-      <c r="O46" s="14" t="inlineStr"/>
-      <c r="P46" s="14" t="inlineStr"/>
-      <c r="Q46" s="14" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr"/>
-      <c r="B47" s="11" t="inlineStr"/>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="N54" s="20" t="inlineStr"/>
+      <c r="O54" s="20" t="inlineStr"/>
+      <c r="P54" s="20" t="inlineStr"/>
+      <c r="Q54" s="20" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr"/>
+      <c r="B55" s="17" t="inlineStr"/>
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D55" s="18" t="inlineStr">
         <is>
           <t>AC-31</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F55" s="18" t="inlineStr">
         <is>
           <t>一覧の表示絞り込みが次回も保持される</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G55" s="18" t="inlineStr">
         <is>
           <t>画面を離れて戻っても列選択が保持（スコープ別）</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>点検のたびに表示条件を選び直すことになる（利便性）</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>localStorage</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J55" s="18" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
+      <c r="K55" s="18" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L55" s="18" t="inlineStr">
         <is>
           <t>§5.3</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
+      <c r="M55" s="18" t="inlineStr">
         <is>
           <t>T-05.png</t>
         </is>
       </c>
-      <c r="N47" s="14" t="inlineStr"/>
-      <c r="O47" s="14" t="inlineStr"/>
-      <c r="P47" s="14" t="inlineStr"/>
-      <c r="Q47" s="14" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="N55" s="20" t="inlineStr"/>
+      <c r="O55" s="20" t="inlineStr"/>
+      <c r="P55" s="20" t="inlineStr"/>
+      <c r="Q55" s="20" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>K-01</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E56" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F56" s="18" t="inlineStr">
         <is>
           <t>権限はロール経由でのみ付与する（人に直接付けない）</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G56" s="18" t="inlineStr">
         <is>
           <t>ユーザー個別に権限内容を編集できるUI・APIが存在しない＝0件</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H56" s="18" t="inlineStr">
         <is>
           <t>人ごとに権限を作り込めてしまい、従業員数だけ設定が増殖して誰が何を見えるか把握できなくなる</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>割当はロールの選択のみ。role_permissions はユーザーに紐付けない</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
+      <c r="J56" s="18" t="inlineStr">
         <is>
           <t>ユーザー割当／割当編集</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr">
+      <c r="K56" s="18" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L48" s="12" t="inlineStr">
+      <c r="L56" s="18" t="inlineStr">
         <is>
           <t>§7-A</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr">
+      <c r="M56" s="18" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N48" s="14" t="inlineStr"/>
-      <c r="O48" s="14" t="inlineStr"/>
-      <c r="P48" s="14" t="inlineStr"/>
-      <c r="Q48" s="14" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr"/>
-      <c r="B49" s="11" t="inlineStr"/>
-      <c r="C49" s="11" t="inlineStr"/>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="N56" s="20" t="inlineStr"/>
+      <c r="O56" s="20" t="inlineStr"/>
+      <c r="P56" s="20" t="inlineStr"/>
+      <c r="Q56" s="20" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr"/>
+      <c r="B57" s="17" t="inlineStr"/>
+      <c r="C57" s="17" t="inlineStr"/>
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>K-02</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F57" s="18" t="inlineStr">
         <is>
           <t>区分とデータ範囲を独立した軸として実装する</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>店舗ロールでも担当店舗を全店・複数店に設定できる＝制約なし</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>「店舗ロール＝自店舗のみ」と固定され、エリアマネージャーや複数店舗所属が表現できない</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>user_roles.store_ids は区分と独立。区分でstore_idsを制限しない</t>
         </is>
       </c>
-      <c r="J49" s="12" t="inlineStr">
+      <c r="J57" s="18" t="inlineStr">
         <is>
           <t>割当編集（対象店舗）</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
+      <c r="K57" s="18" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L49" s="12" t="inlineStr">
+      <c r="L57" s="18" t="inlineStr">
         <is>
           <t>§7-C</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr">
+      <c r="M57" s="18" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N49" s="14" t="inlineStr"/>
-      <c r="O49" s="14" t="inlineStr"/>
-      <c r="P49" s="14" t="inlineStr"/>
-      <c r="Q49" s="14" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr"/>
-      <c r="B50" s="11" t="inlineStr"/>
-      <c r="C50" s="11" t="inlineStr"/>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="N57" s="20" t="inlineStr"/>
+      <c r="O57" s="20" t="inlineStr"/>
+      <c r="P57" s="20" t="inlineStr"/>
+      <c r="Q57" s="20" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="inlineStr"/>
+      <c r="B58" s="17" t="inlineStr"/>
+      <c r="C58" s="17" t="inlineStr"/>
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>K-03</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F58" s="18" t="inlineStr">
         <is>
           <t>操作は登録・編集・削除を一体で扱う</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G58" s="18" t="inlineStr">
         <is>
           <t>権限の状態が なし／閲覧／操作 の3つ＝4つ目が存在しない</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H58" s="18" t="inlineStr">
         <is>
           <t>4状態に戻ると設定コストが跳ね上がり、顧客が使いこなせない</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>role_permissions.level は 0/1/2 のみ。削除専用フラグを作らない</t>
         </is>
       </c>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="J58" s="18" t="inlineStr">
         <is>
           <t>権限編集（権限内容）</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
+      <c r="K58" s="18" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L58" s="18" t="inlineStr">
         <is>
           <t>§7-D / §3.2</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr">
+      <c r="M58" s="18" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N50" s="14" t="inlineStr"/>
-      <c r="O50" s="14" t="inlineStr"/>
-      <c r="P50" s="14" t="inlineStr"/>
-      <c r="Q50" s="14" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr"/>
-      <c r="B51" s="11" t="inlineStr"/>
-      <c r="C51" s="11" t="inlineStr"/>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="N58" s="20" t="inlineStr"/>
+      <c r="O58" s="20" t="inlineStr"/>
+      <c r="P58" s="20" t="inlineStr"/>
+      <c r="Q58" s="20" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr"/>
+      <c r="B59" s="17" t="inlineStr"/>
+      <c r="C59" s="17" t="inlineStr"/>
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>K-04</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F59" s="18" t="inlineStr">
         <is>
           <t>機密ランクを画面に出さない</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G59" s="18" t="inlineStr">
         <is>
           <t>指標一覧・指標条件設定に機密度のバッジ・ラベルが表示されない＝0件</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>顧客が指標を選ぶたびにランクの妥当性を判断させることになる</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>sens は初期値の算出にのみ使用。UIに描画しない</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J59" s="18" t="inlineStr">
         <is>
           <t>指標一覧／指標条件設定</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
+      <c r="K59" s="18" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L51" s="12" t="inlineStr">
+      <c r="L59" s="18" t="inlineStr">
         <is>
           <t>§7-E</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr">
+      <c r="M59" s="18" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N51" s="14" t="inlineStr"/>
-      <c r="O51" s="14" t="inlineStr"/>
-      <c r="P51" s="14" t="inlineStr"/>
-      <c r="Q51" s="14" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr"/>
-      <c r="B52" s="11" t="inlineStr"/>
-      <c r="C52" s="11" t="inlineStr"/>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="N59" s="20" t="inlineStr"/>
+      <c r="O59" s="20" t="inlineStr"/>
+      <c r="P59" s="20" t="inlineStr"/>
+      <c r="Q59" s="20" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr"/>
+      <c r="B60" s="17" t="inlineStr"/>
+      <c r="C60" s="17" t="inlineStr"/>
+      <c r="D60" s="18" t="inlineStr">
         <is>
           <t>K-05</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F60" s="18" t="inlineStr">
         <is>
           <t>会社指標を店舗ロールに付与できる（禁止しない）</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>店舗ロールの指標一覧で会社指標をONにできる。既定はOFF</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>ハードブロックすると「店長にも全社利益を見せたい」という顧客の運用方針を否定する</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>既定OFF＋管理者オプトイン。行スコープ遮断とは独立</t>
         </is>
       </c>
-      <c r="J52" s="12" t="inlineStr">
+      <c r="J60" s="18" t="inlineStr">
         <is>
           <t>指標一覧（会社タブ）</t>
         </is>
       </c>
-      <c r="K52" s="12" t="inlineStr">
+      <c r="K60" s="18" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L52" s="12" t="inlineStr">
+      <c r="L60" s="18" t="inlineStr">
         <is>
           <t>§7-F</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr">
+      <c r="M60" s="18" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N52" s="14" t="inlineStr"/>
-      <c r="O52" s="14" t="inlineStr"/>
-      <c r="P52" s="14" t="inlineStr"/>
-      <c r="Q52" s="14" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr"/>
-      <c r="B53" s="11" t="inlineStr"/>
-      <c r="C53" s="11" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="N60" s="20" t="inlineStr"/>
+      <c r="O60" s="20" t="inlineStr"/>
+      <c r="P60" s="20" t="inlineStr"/>
+      <c r="Q60" s="20" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr"/>
+      <c r="B61" s="17" t="inlineStr"/>
+      <c r="C61" s="17" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>K-06</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F61" s="18" t="inlineStr">
         <is>
           <t>「含める」チェックを店舗選択と統合しない</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G61" s="18" t="inlineStr">
         <is>
           <t>一括割当で店舗を選んだだけでは権限が付与されない</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>誤クリックがそのまま権限付与になり、意図しない人に権限が渡る</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>含めるチェックを明示の安全装置として残す</t>
         </is>
       </c>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="J61" s="18" t="inlineStr">
         <is>
           <t>一括割当</t>
         </is>
       </c>
-      <c r="K53" s="12" t="inlineStr">
+      <c r="K61" s="18" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L53" s="12" t="inlineStr">
+      <c r="L61" s="18" t="inlineStr">
         <is>
           <t>§7-G</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr">
+      <c r="M61" s="18" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N53" s="14" t="inlineStr"/>
-      <c r="O53" s="14" t="inlineStr"/>
-      <c r="P53" s="14" t="inlineStr"/>
-      <c r="Q53" s="14" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="N61" s="20" t="inlineStr"/>
+      <c r="O61" s="20" t="inlineStr"/>
+      <c r="P61" s="20" t="inlineStr"/>
+      <c r="Q61" s="20" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>M8 顧客価値に到達</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>I. 顧客価値に到達しているか</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D62" s="18" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E62" s="19" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F62" s="18" t="inlineStr">
         <is>
           <t>画面単位で表現できる4シナリオの権限が作れる</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t>SC-01経理／SC-02人事／SC-04バイトL／SC-06スタッフ の4件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>顧客が求める権限を作れない＝リリースする意味がない</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>（総合判定）</t>
         </is>
       </c>
-      <c r="J54" s="12" t="inlineStr">
+      <c r="J62" s="18" t="inlineStr">
         <is>
           <t>全画面（6シナリオ）</t>
         </is>
       </c>
-      <c r="K54" s="12" t="inlineStr">
+      <c r="K62" s="18" t="inlineStr">
         <is>
           <t>T-22</t>
         </is>
       </c>
-      <c r="L54" s="12" t="inlineStr">
+      <c r="L62" s="18" t="inlineStr">
         <is>
           <t>§1.2 顧客要望</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr">
+      <c r="M62" s="18" t="inlineStr">
         <is>
           <t>6シナリオの判定表</t>
         </is>
       </c>
-      <c r="N54" s="14" t="inlineStr"/>
-      <c r="O54" s="14" t="inlineStr"/>
-      <c r="P54" s="14" t="inlineStr"/>
-      <c r="Q54" s="14" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="N62" s="20" t="inlineStr"/>
+      <c r="O62" s="20" t="inlineStr"/>
+      <c r="P62" s="20" t="inlineStr"/>
+      <c r="Q62" s="20" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E63" s="24" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F63" s="18" t="inlineStr">
         <is>
           <t>担当外店舗のデータを返さない</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t>他店データ=0件。2店舗合計=表示合計</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>担当外店舗のデータが混ざる。P3（データ範囲の強制）の要否判断に使う</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>P3 行スコープ強制</t>
         </is>
       </c>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="J63" s="18" t="inlineStr">
         <is>
           <t>集計／売上分析</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
+      <c r="K63" s="18" t="inlineStr">
         <is>
           <t>T-11 T-23</t>
         </is>
       </c>
-      <c r="L55" s="12" t="inlineStr">
+      <c r="L63" s="18" t="inlineStr">
         <is>
           <t>§3.1 ④ / §8-6</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr">
+      <c r="M63" s="18" t="inlineStr">
         <is>
           <t>T-11.png</t>
         </is>
       </c>
-      <c r="N55" s="14" t="inlineStr"/>
-      <c r="O55" s="14" t="inlineStr"/>
-      <c r="P55" s="14" t="inlineStr"/>
-      <c r="Q55" s="14" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr"/>
-      <c r="B56" s="11" t="inlineStr"/>
-      <c r="C56" s="11" t="inlineStr"/>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="N63" s="20" t="inlineStr"/>
+      <c r="O63" s="20" t="inlineStr"/>
+      <c r="P63" s="20" t="inlineStr"/>
+      <c r="Q63" s="20" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr"/>
+      <c r="B64" s="17" t="inlineStr"/>
+      <c r="C64" s="17" t="inlineStr"/>
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>AC-24</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
+      <c r="E64" s="24" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F64" s="18" t="inlineStr">
         <is>
           <t>閲覧のみの権限で更新できない</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G64" s="18" t="inlineStr">
         <is>
           <t>保存・登録・削除=不可（値が変わらない）</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>閲覧のみの権限で更新できてしまう。P2の要否判断に使う</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>P2 操作判定</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J64" s="18" t="inlineStr">
         <is>
           <t>費用設定／従業員管理</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
+      <c r="K64" s="18" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="L56" s="12" t="inlineStr">
+      <c r="L64" s="18" t="inlineStr">
         <is>
           <t>§3.1 ② / §8-6</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr">
+      <c r="M64" s="18" t="inlineStr">
         <is>
           <t>T-23.png</t>
         </is>
       </c>
-      <c r="N56" s="14" t="inlineStr"/>
-      <c r="O56" s="14" t="inlineStr"/>
-      <c r="P56" s="14" t="inlineStr"/>
-      <c r="Q56" s="14" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr"/>
-      <c r="B57" s="11" t="inlineStr"/>
-      <c r="C57" s="11" t="inlineStr"/>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="N64" s="20" t="inlineStr"/>
+      <c r="O64" s="20" t="inlineStr"/>
+      <c r="P64" s="20" t="inlineStr"/>
+      <c r="Q64" s="20" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr"/>
+      <c r="B65" s="17" t="inlineStr"/>
+      <c r="C65" s="17" t="inlineStr"/>
+      <c r="D65" s="18" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="E65" s="24" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F65" s="18" t="inlineStr">
         <is>
           <t>許可していない指標を表示しない</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G65" s="18" t="inlineStr">
         <is>
           <t>ダッシュボード・分析画面に非許可指標=0件</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H65" s="18" t="inlineStr">
         <is>
           <t>許可外の指標が表示される。P4の要否判断に使う</t>
         </is>
       </c>
-      <c r="I57" s="12" t="inlineStr">
+      <c r="I65" s="18" t="inlineStr">
         <is>
           <t>P4 指標可視性</t>
         </is>
       </c>
-      <c r="J57" s="12" t="inlineStr">
+      <c r="J65" s="18" t="inlineStr">
         <is>
           <t>ダッシュボード／分析画面</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
+      <c r="K65" s="18" t="inlineStr">
         <is>
           <t>T-19 T-23</t>
         </is>
       </c>
-      <c r="L57" s="12" t="inlineStr">
+      <c r="L65" s="18" t="inlineStr">
         <is>
           <t>§3.1 ③ / §5.5</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr">
+      <c r="M65" s="18" t="inlineStr">
         <is>
           <t>T-19.png</t>
         </is>
       </c>
-      <c r="N57" s="14" t="inlineStr"/>
-      <c r="O57" s="14" t="inlineStr"/>
-      <c r="P57" s="14" t="inlineStr"/>
-      <c r="Q57" s="14" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr"/>
-      <c r="B58" s="11" t="inlineStr"/>
-      <c r="C58" s="11" t="inlineStr"/>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="N65" s="20" t="inlineStr"/>
+      <c r="O65" s="20" t="inlineStr"/>
+      <c r="P65" s="20" t="inlineStr"/>
+      <c r="Q65" s="20" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="inlineStr"/>
+      <c r="B66" s="17" t="inlineStr"/>
+      <c r="C66" s="17" t="inlineStr"/>
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>AC-26</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E66" s="24" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="F66" s="18" t="inlineStr">
         <is>
           <t>変更が監査ログに残る</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G66" s="18" t="inlineStr">
         <is>
           <t>誰がいつ何を変えたか追える</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>変更履歴が残らない。P5の要否判断に使う</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>P5 audit_logs</t>
         </is>
       </c>
-      <c r="J58" s="12" t="inlineStr">
+      <c r="J66" s="18" t="inlineStr">
         <is>
           <t>（管理画面のログ）</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr">
+      <c r="K66" s="18" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="L58" s="12" t="inlineStr">
+      <c r="L66" s="18" t="inlineStr">
         <is>
           <t>§6 audit_logs</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr">
+      <c r="M66" s="18" t="inlineStr">
         <is>
           <t>T-23.png</t>
         </is>
       </c>
-      <c r="N58" s="14" t="inlineStr"/>
-      <c r="O58" s="14" t="inlineStr"/>
-      <c r="P58" s="14" t="inlineStr"/>
-      <c r="Q58" s="14" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr"/>
-      <c r="B59" s="11" t="inlineStr"/>
-      <c r="C59" s="11" t="inlineStr"/>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="N66" s="20" t="inlineStr"/>
+      <c r="O66" s="20" t="inlineStr"/>
+      <c r="P66" s="20" t="inlineStr"/>
+      <c r="Q66" s="20" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="inlineStr"/>
+      <c r="B67" s="17" t="inlineStr"/>
+      <c r="C67" s="17" t="inlineStr"/>
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>AC-32</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="E67" s="24" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F67" s="18" t="inlineStr">
         <is>
           <t>データ範囲・操作を要する権限が作れる</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>データ範囲・操作を要する権限が作れない。P2/P3の前倒し判断に使う</t>
         </is>
       </c>
-      <c r="I59" s="12" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
         <is>
           <t>P2／P3</t>
         </is>
       </c>
-      <c r="J59" s="12" t="inlineStr">
+      <c r="J67" s="18" t="inlineStr">
         <is>
           <t>全画面（SC-03／SC-05）</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr">
+      <c r="K67" s="18" t="inlineStr">
         <is>
           <t>T-22 T-23</t>
         </is>
       </c>
-      <c r="L59" s="12" t="inlineStr">
+      <c r="L67" s="18" t="inlineStr">
         <is>
           <t>§1.2 顧客要望 / §8-6</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr">
+      <c r="M67" s="18" t="inlineStr">
         <is>
           <t>T-22.png</t>
         </is>
       </c>
-      <c r="N59" s="14" t="inlineStr"/>
-      <c r="O59" s="14" t="inlineStr"/>
-      <c r="P59" s="14" t="inlineStr"/>
-      <c r="Q59" s="14" t="inlineStr"/>
+      <c r="N67" s="20" t="inlineStr"/>
+      <c r="O67" s="20" t="inlineStr"/>
+      <c r="P67" s="20" t="inlineStr"/>
+      <c r="Q67" s="20" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A20:Q59"/>
-  <mergeCells count="1">
-    <mergeCell ref="B15:H15"/>
+  <autoFilter ref="A28:Q67"/>
+  <mergeCells count="18">
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
-  <conditionalFormatting sqref="N21:N59">
+  <conditionalFormatting sqref="N29:N67">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"NG"</formula>
     </cfRule>
@@ -3524,16 +3770,16 @@
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H14">
+  <conditionalFormatting sqref="J17:J25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"完了"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="0">
-      <formula>LEFT(H6,2)="未達"</formula>
+      <formula>LEFT(J17,2)="未達"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N21:N59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N29:N67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -599,7 +599,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>新規追加画面が全ロールで なし</t>
+          <t>新規追加した画面が全ロールで「なし」＝例外0件</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>権限テンプレートが適用でき権限一覧に登録される。下書きの一時保存で復元、破棄で初期化できる</t>
+          <t>権限テンプレートの適用で推奨4権限が権限一覧に登録される＝4件。一時保存→再訪で選択状態が一致、破棄で既定に戻る</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>全項目オフのロールでログインでき着地画面が出る</t>
+          <t>全項目オフのロールでログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ0件</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>即時または再ログインで反映（無反映はNG）</t>
+          <t>設定変更後、対象ユーザーの次の画面遷移または再ログインで反映される。無反映＝0件（どちらの方式かは記録する）</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>エラーまたは警告が出る</t>
+          <t>担当店舗0件のまま保存できない、または警告が出る。無警告のまま保存できる＝0件</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>権限設定を自ロールから外す操作が警告またはブロック</t>
+          <t>権限設定を自ロールから外す操作でブロックまたは警告が出る。無警告で保存できる＝0件</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>指標管理に編集UIが出ない。付与先指定はオーナーのみ実行可</t>
+          <t>指標管理に編集UI（トグル／コピー／条件設定）が表示される＝0件。オーナー以外が付与先指定を実行できる＝0件</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>画面を離れて戻っても列選択が保持（スコープ別）</t>
+          <t>画面を離れて戻ったとき、列選択が離脱前と一致（スコープ別に保持）</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>店舗ロールの指標一覧で会社指標をONにできる。既定はOFF</t>
+          <t>店舗ロールの指標一覧で会社指標をONにできる（ハードブロック＝0件）。初期状態のON件数は 従業員=会社0／店長=会社8</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>誰がいつ何を変えたか追える</t>
+          <t>権限の作成・割当の変更が操作ログに記録される＝記録漏れ0件（P1では実測を記録するのみ）</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$17:$Q$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$17:$Q$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -684,15 +684,15 @@
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4">
-        <f>COUNTIF($A$18:$A$56,A5)</f>
+        <f>COUNTIF($A$18:$A$57,A5)</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>COUNTIFS($A$18:$A$56,A5,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A5,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>COUNTIFS($A$18:$A$56,A5,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A5,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -722,15 +722,15 @@
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4">
-        <f>COUNTIF($A$18:$A$56,A6)</f>
+        <f>COUNTIF($A$18:$A$57,A6)</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>COUNTIFS($A$18:$A$56,A6,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A6,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>COUNTIFS($A$18:$A$56,A6,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A6,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -760,15 +760,15 @@
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4">
-        <f>COUNTIF($A$18:$A$56,A7)</f>
+        <f>COUNTIF($A$18:$A$57,A7)</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>COUNTIFS($A$18:$A$56,A7,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A7,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>COUNTIFS($A$18:$A$56,A7,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A7,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -798,15 +798,15 @@
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4">
-        <f>COUNTIF($A$18:$A$56,A8)</f>
+        <f>COUNTIF($A$18:$A$57,A8)</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>COUNTIFS($A$18:$A$56,A8,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A8,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="4">
-        <f>COUNTIFS($A$18:$A$56,A8,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A8,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -836,15 +836,15 @@
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4">
-        <f>COUNTIF($A$18:$A$56,A9)</f>
+        <f>COUNTIF($A$18:$A$57,A9)</f>
         <v/>
       </c>
       <c r="F9" s="4">
-        <f>COUNTIFS($A$18:$A$56,A9,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A9,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="4">
-        <f>COUNTIFS($A$18:$A$56,A9,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A9,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -874,15 +874,15 @@
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4">
-        <f>COUNTIF($A$18:$A$56,A10)</f>
+        <f>COUNTIF($A$18:$A$57,A10)</f>
         <v/>
       </c>
       <c r="F10" s="4">
-        <f>COUNTIFS($A$18:$A$56,A10,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A10,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="4">
-        <f>COUNTIFS($A$18:$A$56,A10,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A10,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -912,15 +912,15 @@
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4">
-        <f>COUNTIF($A$18:$A$56,A11)</f>
+        <f>COUNTIF($A$18:$A$57,A11)</f>
         <v/>
       </c>
       <c r="F11" s="4">
-        <f>COUNTIFS($A$18:$A$56,A11,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A11,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G11" s="4">
-        <f>COUNTIFS($A$18:$A$56,A11,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A11,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -950,15 +950,15 @@
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4">
-        <f>COUNTIF($A$18:$A$56,A12)</f>
+        <f>COUNTIF($A$18:$A$57,A12)</f>
         <v/>
       </c>
       <c r="F12" s="4">
-        <f>COUNTIFS($A$18:$A$56,A12,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A12,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G12" s="4">
-        <f>COUNTIFS($A$18:$A$56,A12,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A12,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -988,15 +988,15 @@
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4">
-        <f>COUNTIF($A$18:$A$56,A13)</f>
+        <f>COUNTIF($A$18:$A$57,A13)</f>
         <v/>
       </c>
       <c r="F13" s="4">
-        <f>COUNTIFS($A$18:$A$56,A13,$N$18:$N$56,"OK")</f>
+        <f>COUNTIFS($A$18:$A$57,A13,$N$18:$N$57,"OK")</f>
         <v/>
       </c>
       <c r="G13" s="4">
-        <f>COUNTIFS($A$18:$A$56,A13,$N$18:$N$56,"NG")</f>
+        <f>COUNTIFS($A$18:$A$57,A13,$N$18:$N$57,"NG")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>IF(COUNTIFS($E$18:$E$56,"MVP必須",$N$18:$N$56,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$18:$E$56,"MVP必須",$N$18:$N$56,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$18:$E$56,"MVP必須")-COUNTIFS($E$18:$E$56,"MVP必須",$N$18:$N$56,"OK")-COUNTIFS($E$18:$E$56,"MVP必須",$N$18:$N$56,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$18:$E$56,"MVP必須")-COUNTIFS($E$18:$E$56,"MVP必須",$N$18:$N$56,"OK")-COUNTIFS($E$18:$E$56,"MVP必須",$N$18:$N$56,"NG"))&amp;"件）",IF(COUNTIFS($E$18:$E$56,"品質必須",$N$18:$N$56,"NG")&gt;0,"MVP到達。品質必須にNGあり ── 運用でカバーできるかPdMが判断","MVP到達・品質必須も充足 ── リリース可")))</f>
+        <f>IF(COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$18:$E$57,"MVP必須")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"OK")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$18:$E$57,"MVP必須")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"OK")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG"))&amp;"件）",IF(COUNTIFS($E$18:$E$57,"品質必須",$N$18:$N$57,"NG")&gt;0,"MVP到達。品質必須にNGあり ── 運用でカバーできるかPdMが判断","MVP到達・品質必須も充足 ── リリース可")))</f>
         <v/>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>SC-01経理／SC-02人事／SC-04バイトL／SC-06スタッフ の4件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
+          <t>SC-01a経理（会社）／SC-01b経理（店舗）／SC-02人事／SC-04バイトL／SC-06スタッフ の5件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -3887,8 +3887,79 @@
       <c r="P56" s="15" t="inlineStr"/>
       <c r="Q56" s="15" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>M9 次段階（P1対象外）</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>J. 次段階（P1では実装しない）</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>AC-34</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="inlineStr">
+        <is>
+          <t>次段階</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>会社画面と店舗画面の両方を扱う権限が作れる</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>1人の権限で 会社画面（お支払い等）と店舗画面（費用設定等）の両方が開ける＝現状は×が想定</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>経理のように会社の支払と店舗の費用設定を両方見る職務が、1人1ロールでは表現できず権限を2つ作って人を分ける運用になる</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>user_roles（1人1ロール）／区分の設計</t>
+        </is>
+      </c>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>権限編集（区分）</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>T-09 T-09b</t>
+        </is>
+      </c>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>§3.5 / §7-C 区分とデータ範囲は独立した別軸</t>
+        </is>
+      </c>
+      <c r="M57" s="13" t="inlineStr">
+        <is>
+          <t>T-09b.png</t>
+        </is>
+      </c>
+      <c r="N57" s="15" t="inlineStr"/>
+      <c r="O57" s="15" t="inlineStr"/>
+      <c r="P57" s="15" t="inlineStr"/>
+      <c r="Q57" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A17:Q56"/>
+  <autoFilter ref="A17:Q57"/>
   <mergeCells count="10">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
@@ -3901,7 +3972,7 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
-  <conditionalFormatting sqref="N18:N56">
+  <conditionalFormatting sqref="N18:N57">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"NG"</formula>
     </cfRule>
@@ -3918,7 +3989,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N18:N56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N18:N57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$17:$Q$57</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,50 +28,19 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E5F"/>
-      <sz val="15"/>
+      <sz val="13"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="005B6B7C"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B23B32"/>
-      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E5F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="001F4E5F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="009AA7B0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00B9C4CC"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -82,42 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F1F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEF6FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F3F5"/>
+        <fgColor rgb="001F7A8C"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,100 +63,60 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
-      <font>
-        <b val="1"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F8B4AE"/>
+          <fgColor rgb="00D8F0E0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00BFE5CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00BFE5CC"/>
+          <fgColor rgb="00FBDCDC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -593,23 +485,23 @@
   <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -622,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「合否」に OK / NG を入れると下の到達状況が自動更新されます。用語の定義は 20260804_権限設定_00_定義表.xlsx を参照。</t>
+          <t>「合否」に OK / NG を入れると下の到達状況が自動で集計されます。判定は上のマイルストーン順に進めてください。</t>
         </is>
       </c>
     </row>
@@ -637,8 +529,8 @@
           <t>完了条件</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>条件数</t>
@@ -659,14 +551,9 @@
           <t>未判定</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>到達率</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>状態</t>
         </is>
       </c>
     </row>
@@ -676,26 +563,26 @@
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4">
-        <f>COUNTIF($A$18:$A$57,A5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>COUNTIFS($A$18:$A$57,A5,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G5" s="4">
-        <f>COUNTIFS($A$18:$A$57,A5,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H5" s="4">
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5">
+        <f>COUNTIF($A$17:$A$57,A5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>COUNTIFS($A$17:$A$57,A5,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G5" s="5">
+        <f>COUNTIFS($A$17:$A$57,A5,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
         <f>E5-F5-G5</f>
         <v/>
       </c>
@@ -703,10 +590,6 @@
         <f>IF(E5=0,"",F5/E5)</f>
         <v/>
       </c>
-      <c r="J5" s="4">
-        <f>IF(G5&gt;0,"未達（NG "&amp;G5&amp;"件）",IF(H5&gt;0,"進行中（残 "&amp;H5&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -714,26 +597,26 @@
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4">
-        <f>COUNTIF($A$18:$A$57,A6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="4">
-        <f>COUNTIFS($A$18:$A$57,A6,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4">
-        <f>COUNTIFS($A$18:$A$57,A6,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4">
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5">
+        <f>COUNTIF($A$17:$A$57,A6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="5">
+        <f>COUNTIFS($A$17:$A$57,A6,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>COUNTIFS($A$17:$A$57,A6,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H6" s="5">
         <f>E6-F6-G6</f>
         <v/>
       </c>
@@ -741,10 +624,6 @@
         <f>IF(E6=0,"",F6/E6)</f>
         <v/>
       </c>
-      <c r="J6" s="4">
-        <f>IF(G6&gt;0,"未達（NG "&amp;G6&amp;"件）",IF(H6&gt;0,"進行中（残 "&amp;H6&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -752,26 +631,26 @@
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4">
-        <f>COUNTIF($A$18:$A$57,A7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="4">
-        <f>COUNTIFS($A$18:$A$57,A7,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G7" s="4">
-        <f>COUNTIFS($A$18:$A$57,A7,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H7" s="4">
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5">
+        <f>COUNTIF($A$17:$A$57,A7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>COUNTIFS($A$17:$A$57,A7,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>COUNTIFS($A$17:$A$57,A7,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
         <f>E7-F7-G7</f>
         <v/>
       </c>
@@ -779,10 +658,6 @@
         <f>IF(E7=0,"",F7/E7)</f>
         <v/>
       </c>
-      <c r="J7" s="4">
-        <f>IF(G7&gt;0,"未達（NG "&amp;G7&amp;"件）",IF(H7&gt;0,"進行中（残 "&amp;H7&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -790,26 +665,26 @@
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4">
-        <f>COUNTIF($A$18:$A$57,A8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="4">
-        <f>COUNTIFS($A$18:$A$57,A8,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G8" s="4">
-        <f>COUNTIFS($A$18:$A$57,A8,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H8" s="4">
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5">
+        <f>COUNTIF($A$17:$A$57,A8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>COUNTIFS($A$17:$A$57,A8,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>COUNTIFS($A$17:$A$57,A8,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
         <f>E8-F8-G8</f>
         <v/>
       </c>
@@ -817,10 +692,6 @@
         <f>IF(E8=0,"",F8/E8)</f>
         <v/>
       </c>
-      <c r="J8" s="4">
-        <f>IF(G8&gt;0,"未達（NG "&amp;G8&amp;"件）",IF(H8&gt;0,"進行中（残 "&amp;H8&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -828,26 +699,26 @@
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4">
-        <f>COUNTIF($A$18:$A$57,A9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="4">
-        <f>COUNTIFS($A$18:$A$57,A9,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G9" s="4">
-        <f>COUNTIFS($A$18:$A$57,A9,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H9" s="4">
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5">
+        <f>COUNTIF($A$17:$A$57,A9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="5">
+        <f>COUNTIFS($A$17:$A$57,A9,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G9" s="5">
+        <f>COUNTIFS($A$17:$A$57,A9,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H9" s="5">
         <f>E9-F9-G9</f>
         <v/>
       </c>
@@ -855,10 +726,6 @@
         <f>IF(E9=0,"",F9/E9)</f>
         <v/>
       </c>
-      <c r="J9" s="4">
-        <f>IF(G9&gt;0,"未達（NG "&amp;G9&amp;"件）",IF(H9&gt;0,"進行中（残 "&amp;H9&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -866,26 +733,26 @@
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4">
-        <f>COUNTIF($A$18:$A$57,A10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="4">
-        <f>COUNTIFS($A$18:$A$57,A10,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G10" s="4">
-        <f>COUNTIFS($A$18:$A$57,A10,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H10" s="4">
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5">
+        <f>COUNTIF($A$17:$A$57,A10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>COUNTIFS($A$17:$A$57,A10,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>COUNTIFS($A$17:$A$57,A10,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H10" s="5">
         <f>E10-F10-G10</f>
         <v/>
       </c>
@@ -893,10 +760,6 @@
         <f>IF(E10=0,"",F10/E10)</f>
         <v/>
       </c>
-      <c r="J10" s="4">
-        <f>IF(G10&gt;0,"未達（NG "&amp;G10&amp;"件）",IF(H10&gt;0,"進行中（残 "&amp;H10&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -904,26 +767,26 @@
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4">
-        <f>COUNTIF($A$18:$A$57,A11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="4">
-        <f>COUNTIFS($A$18:$A$57,A11,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G11" s="4">
-        <f>COUNTIFS($A$18:$A$57,A11,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H11" s="4">
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5">
+        <f>COUNTIF($A$17:$A$57,A11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>COUNTIFS($A$17:$A$57,A11,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G11" s="5">
+        <f>COUNTIFS($A$17:$A$57,A11,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H11" s="5">
         <f>E11-F11-G11</f>
         <v/>
       </c>
@@ -931,10 +794,6 @@
         <f>IF(E11=0,"",F11/E11)</f>
         <v/>
       </c>
-      <c r="J11" s="4">
-        <f>IF(G11&gt;0,"未達（NG "&amp;G11&amp;"件）",IF(H11&gt;0,"進行中（残 "&amp;H11&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -942,26 +801,26 @@
           <t>M8 顧客価値に到達</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4">
-        <f>COUNTIF($A$18:$A$57,A12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="4">
-        <f>COUNTIFS($A$18:$A$57,A12,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G12" s="4">
-        <f>COUNTIFS($A$18:$A$57,A12,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H12" s="4">
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5">
+        <f>COUNTIF($A$17:$A$57,A12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>COUNTIFS($A$17:$A$57,A12,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>COUNTIFS($A$17:$A$57,A12,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H12" s="5">
         <f>E12-F12-G12</f>
         <v/>
       </c>
@@ -969,10 +828,6 @@
         <f>IF(E12=0,"",F12/E12)</f>
         <v/>
       </c>
-      <c r="J12" s="4">
-        <f>IF(G12&gt;0,"未達（NG "&amp;G12&amp;"件）",IF(H12&gt;0,"進行中（残 "&amp;H12&amp;"件）","完了"))</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -980,26 +835,26 @@
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4">
-        <f>COUNTIF($A$18:$A$57,A13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
-        <f>COUNTIFS($A$18:$A$57,A13,$N$18:$N$57,"OK")</f>
-        <v/>
-      </c>
-      <c r="G13" s="4">
-        <f>COUNTIFS($A$18:$A$57,A13,$N$18:$N$57,"NG")</f>
-        <v/>
-      </c>
-      <c r="H13" s="4">
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5">
+        <f>COUNTIF($A$17:$A$57,A13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="5">
+        <f>COUNTIFS($A$17:$A$57,A13,$N$17:$N$57,"OK")</f>
+        <v/>
+      </c>
+      <c r="G13" s="5">
+        <f>COUNTIFS($A$17:$A$57,A13,$N$17:$N$57,"NG")</f>
+        <v/>
+      </c>
+      <c r="H13" s="5">
         <f>E13-F13-G13</f>
         <v/>
       </c>
@@ -1007,2989 +862,3016 @@
         <f>IF(E13=0,"",F13/E13)</f>
         <v/>
       </c>
-      <c r="J13" s="4">
-        <f>IF(G13&gt;0,"未達（NG "&amp;G13&amp;"件）",IF(H13&gt;0,"進行中（残 "&amp;H13&amp;"件）","完了"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>総合判定</t>
-        </is>
-      </c>
-      <c r="B14" s="8">
-        <f>IF(COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$18:$E$57,"MVP必須")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"OK")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$18:$E$57,"MVP必須")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"OK")-COUNTIFS($E$18:$E$57,"MVP必須",$N$18:$N$57,"NG"))&amp;"件）",IF(COUNTIFS($E$18:$E$57,"品質必須",$N$18:$N$57,"NG")&gt;0,"MVP到達。品質必須にNGあり ── 運用でカバーできるかPdMが判断","MVP到達・品質必須も充足 ── リリース可")))</f>
-        <v/>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>マイルストーンの完了条件</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>設計ポイント</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>条件ID</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>実装レベル</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>何を実装するか</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>合格ライン（この数値を満たせば実装完了）</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>実装できていないと起きること</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>実装箇所</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>確認する画面</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>対応検証ID</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>仕様書の根拠</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>エビデンス</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>実測値</t>
         </is>
       </c>
-      <c r="P17" s="9" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>判定者</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>会社／店舗の区分で、設定対象の画面を出し分ける</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリが設定対象に出る</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>会社用・店舗用の権限を別々に作れない。機能の前提が崩れる</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>権限編集（区分の選択→権限内容）</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>権限編集（区分の切替）</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>§3.3 カテゴリ構成</t>
         </is>
       </c>
-      <c r="M18" s="13" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>T-03.png</t>
         </is>
       </c>
-      <c r="N18" s="15" t="inlineStr"/>
-      <c r="O18" s="15" t="inlineStr"/>
-      <c r="P18" s="15" t="inlineStr"/>
-      <c r="Q18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
+      <c r="P17" s="8" t="inlineStr"/>
+      <c r="Q17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>区分に該当しない画面を設定対象に出さない</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>会社で店舗専用6が出ない、店舗で会社専用4が出ない</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>会社の権限に店舗専用画面が出るなど、設定時に誤った選択肢を選べてしまう</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>権限編集（カテゴリの ctx 判定）</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>権限編集（権限内容）</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>§3.3</t>
         </is>
       </c>
-      <c r="M19" s="13" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>T-03.png</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr"/>
-      <c r="O19" s="15" t="inlineStr"/>
-      <c r="P19" s="15" t="inlineStr"/>
-      <c r="Q19" s="15" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="N18" s="8" t="inlineStr"/>
+      <c r="O18" s="8" t="inlineStr"/>
+      <c r="P18" s="8" t="inlineStr"/>
+      <c r="Q18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>権限の作成・保存・再表示が往復して壊れない</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>保存→再表示で欠落・反転=0件</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>設定した権限が保存されない。機能として成立しない</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>権限編集／roles・role_permissions</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>権限編集（保存→再表示）</t>
         </is>
       </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
       </c>
-      <c r="L20" s="13" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>§5.2 権限編集</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr"/>
-      <c r="O20" s="15" t="inlineStr"/>
-      <c r="P20" s="15" t="inlineStr"/>
-      <c r="Q20" s="15" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
+      <c r="P19" s="8" t="inlineStr"/>
+      <c r="Q19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>AC-08</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>雛形（ベース）から差分で作れる。移植プリセットを候補に出す</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>ベース選択に4種（オーナー相当/本部管理/店長/従業員）＋プレーンが出る。エリア長は含まれない</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>27画面をゼロから設定することになり、実運用が回らない</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>権限編集①ベース選択</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>権限編集（＋権限を新規作成）</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="L21" s="13" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>§5.2 / §7-H' エリア長を既定テンプレートにしない（2026-08-04）</t>
         </is>
       </c>
-      <c r="M21" s="13" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>T-01.png</t>
         </is>
       </c>
-      <c r="N21" s="15" t="inlineStr"/>
-      <c r="O21" s="15" t="inlineStr"/>
-      <c r="P21" s="15" t="inlineStr"/>
-      <c r="Q21" s="15" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="N20" s="8" t="inlineStr"/>
+      <c r="O20" s="8" t="inlineStr"/>
+      <c r="P20" s="8" t="inlineStr"/>
+      <c r="Q20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>AC-09</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>ゼロから作る場合は全項目オフで始まる</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>プレーン選択時に許可=0件</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>意図せず開いた状態の権限ができる</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>権限編集（プレーン）</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>権限編集（プレーン選択時）</t>
         </is>
       </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>§5.2</t>
         </is>
       </c>
-      <c r="M22" s="13" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>T-02.png</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr"/>
-      <c r="O22" s="15" t="inlineStr"/>
-      <c r="P22" s="15" t="inlineStr"/>
-      <c r="Q22" s="15" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
+      <c r="P21" s="8" t="inlineStr"/>
+      <c r="Q21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>AC-12</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>権限が未定義の画面は既定で塞ぐ（fail-closed）</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>新規追加した画面が全ロールで「なし」＝例外0件</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>今後追加される画面が全権限に開いた状態で出る</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>判定層の既定値</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>権限編集</t>
         </is>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>§9 fail-closed</t>
         </is>
       </c>
-      <c r="M23" s="13" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>T-02.png</t>
         </is>
       </c>
-      <c r="N23" s="15" t="inlineStr"/>
-      <c r="O23" s="15" t="inlineStr"/>
-      <c r="P23" s="15" t="inlineStr"/>
-      <c r="Q23" s="15" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="N22" s="8" t="inlineStr"/>
+      <c r="O22" s="8" t="inlineStr"/>
+      <c r="P22" s="8" t="inlineStr"/>
+      <c r="Q22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>導入時に推奨権限をまとめて登録できる（下書きの保存・破棄を含む）</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>権限テンプレートの適用で推奨4権限が権限一覧に登録される＝4件。一時保存→再訪で選択状態が一致、破棄で既定に戻る</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>導入時に権限を用意できず、導入作業そのものが始められない</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>権限テンプレート画面</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>権限テンプレート</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="L24" s="13" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>§5.6 F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="M24" s="13" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>T-04.png</t>
         </is>
       </c>
-      <c r="N24" s="15" t="inlineStr"/>
-      <c r="O24" s="15" t="inlineStr"/>
-      <c r="P24" s="15" t="inlineStr"/>
-      <c r="Q24" s="15" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
+      <c r="P23" s="8" t="inlineStr"/>
+      <c r="Q23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>許可した画面が開ける</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>見えるべき画面=100%開ける</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>必要な画面が開けず現場の業務が止まる</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>各画面の表示判定</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>全画面（各権限でログイン）</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>T-09〜T-14</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t>§3.1 ①画面</t>
         </is>
       </c>
-      <c r="M25" s="13" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>T-09.png</t>
         </is>
       </c>
-      <c r="N25" s="15" t="inlineStr"/>
-      <c r="O25" s="15" t="inlineStr"/>
-      <c r="P25" s="15" t="inlineStr"/>
-      <c r="Q25" s="15" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="N24" s="8" t="inlineStr"/>
+      <c r="O24" s="8" t="inlineStr"/>
+      <c r="P24" s="8" t="inlineStr"/>
+      <c r="Q24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>許可していない画面が開けない。メニュー非表示だけでなく直URLも塞ぐ</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>メニュー非表示かつ直URLでも開けない=100%</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>見せてはいけない画面が見える＝情報漏洩</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>コントローラの認可（メニュー生成だけでは不可）</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>全画面（直URLを含む）</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>T-09〜T-14</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>§9 誤って通す</t>
         </is>
       </c>
-      <c r="M26" s="13" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>T-09.png</t>
         </is>
       </c>
-      <c r="N26" s="15" t="inlineStr"/>
-      <c r="O26" s="15" t="inlineStr"/>
-      <c r="P26" s="15" t="inlineStr"/>
-      <c r="Q26" s="15" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>権限を最小にしてもログインでき、ランディングに着地する</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>全項目オフのロールでログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ0件</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>権限を絞ると使えなくなる＝絞る運用そのものができない</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>ダッシュボード＝閲覧固定</t>
         </is>
       </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>ダッシュボード</t>
         </is>
       </c>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="L27" s="13" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>§9 誤って塞ぐ</t>
         </is>
       </c>
-      <c r="M27" s="13" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>T-14.png</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr"/>
-      <c r="O27" s="15" t="inlineStr"/>
-      <c r="P27" s="15" t="inlineStr"/>
-      <c r="Q27" s="15" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr"/>
+      <c r="O26" s="8" t="inlineStr"/>
+      <c r="P26" s="8" t="inlineStr"/>
+      <c r="Q26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>設定変更が反映される（即時または再ログイン）</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>設定変更後、対象ユーザーの次の画面遷移または再ログインで反映される。無反映＝0件（どちらの方式かは記録する）</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>権限を変更しても効かない</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>権限のキャッシュ・セッション</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>全画面（変更後に遷移）</t>
         </is>
       </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>T-08</t>
         </is>
       </c>
-      <c r="L28" s="13" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>§8-6</t>
         </is>
       </c>
-      <c r="M28" s="13" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>T-08.png</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr"/>
-      <c r="O28" s="15" t="inlineStr"/>
-      <c r="P28" s="15" t="inlineStr"/>
-      <c r="Q28" s="15" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="8" t="inlineStr"/>
+      <c r="Q27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28" ht="76" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>既存の全管理者に権限が割り当たる（移行漏れ0）</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>ロール未割当=0名</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>権限が付いていない管理者はログインしても何も見えない</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>移行処理</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>ユーザー割当</t>
         </is>
       </c>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>T-18 T-21</t>
         </is>
       </c>
-      <c r="L29" s="13" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M29" s="13" t="inlineStr">
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>ユーザー割当一覧のスクショ（未割当0名）</t>
         </is>
       </c>
-      <c r="N29" s="15" t="inlineStr"/>
-      <c r="O29" s="15" t="inlineStr"/>
-      <c r="P29" s="15" t="inlineStr"/>
-      <c r="Q29" s="15" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="N28" s="8" t="inlineStr"/>
+      <c r="O28" s="8" t="inlineStr"/>
+      <c r="P28" s="8" t="inlineStr"/>
+      <c r="Q28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>AC-14</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>1人1ロール。付け替えで前の権限が確実に外れる</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>割当編集で同時に選べる権限=1つ。付け替えで前の権限の画面=0件</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>前の権限が残り、想定外の画面が見えたままになる</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>割当編集／user_roles</t>
         </is>
       </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>割当編集</t>
         </is>
       </c>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>S-05 T-15</t>
         </is>
       </c>
-      <c r="L30" s="13" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>§3.5 / §7-H 1人1ロール（2026-08-03・暫定）</t>
         </is>
       </c>
-      <c r="M30" s="13" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="N30" s="15" t="inlineStr"/>
-      <c r="O30" s="15" t="inlineStr"/>
-      <c r="P30" s="15" t="inlineStr"/>
-      <c r="Q30" s="15" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="8" t="inlineStr"/>
+      <c r="Q29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="76" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>付け替えで既存権限が置き換わることを事前に明示する</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>登録済み/置換予告が該当行に表示=100%</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>付け替えで意図せず権限を剥奪してしまう</t>
         </is>
       </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>割当編集／一括割当のUI</t>
         </is>
       </c>
-      <c r="J31" s="13" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>割当編集／一括割当</t>
         </is>
       </c>
-      <c r="K31" s="13" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>T-15 T-16</t>
         </is>
       </c>
-      <c r="L31" s="13" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>§5.4 事故防止3点</t>
         </is>
       </c>
-      <c r="M31" s="13" t="inlineStr">
+      <c r="M30" s="8" t="inlineStr">
         <is>
           <t>T-15.png</t>
         </is>
       </c>
-      <c r="N31" s="15" t="inlineStr"/>
-      <c r="O31" s="15" t="inlineStr"/>
-      <c r="P31" s="15" t="inlineStr"/>
-      <c r="Q31" s="15" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="8" t="inlineStr"/>
+      <c r="P30" s="8" t="inlineStr"/>
+      <c r="Q30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>担当店舗を複数紐付けられる（人ごとに異なる範囲）</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>店長ベースで作った権限に2店舗を紐付けて保存できる</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>エリアマネージャーなど複数店舗を担当する権限が作れない</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>割当編集（store_ids）</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>割当編集（対象店舗）</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>S-05 T-11</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>§3.1④ / §7-B 担当店舗は割当側にのみ持たせる</t>
         </is>
       </c>
-      <c r="M32" s="13" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="N32" s="15" t="inlineStr"/>
-      <c r="O32" s="15" t="inlineStr"/>
-      <c r="P32" s="15" t="inlineStr"/>
-      <c r="Q32" s="15" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32" ht="76" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>店舗ロールで担当店舗が未設定の割当を検知する</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>担当店舗0件のまま保存できない、または警告が出る。無警告のまま保存できる＝0件</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>担当店舗が未設定のまま割り当てられ、何も見えない人ができる</t>
         </is>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>割当編集のバリデーション</t>
         </is>
       </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>割当編集</t>
         </is>
       </c>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="L33" s="13" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>§5.4</t>
         </is>
       </c>
-      <c r="M33" s="13" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>T-18.png</t>
         </is>
       </c>
-      <c r="N33" s="15" t="inlineStr"/>
-      <c r="O33" s="15" t="inlineStr"/>
-      <c r="P33" s="15" t="inlineStr"/>
-      <c r="Q33" s="15" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="N32" s="8" t="inlineStr"/>
+      <c r="O32" s="8" t="inlineStr"/>
+      <c r="P32" s="8" t="inlineStr"/>
+      <c r="Q32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33" ht="76" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>master と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>適用前後で見える画面の増減=0</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>既存の master 権限で見える画面が増減する。増えれば情報漏洩、減れば業務停止</t>
         </is>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J34" s="13" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>全画面（master でログイン）</t>
         </is>
       </c>
-      <c r="K34" s="13" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L34" s="13" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>§4 段階導入</t>
         </is>
       </c>
-      <c r="M34" s="13" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N34" s="15" t="inlineStr"/>
-      <c r="O34" s="15" t="inlineStr"/>
-      <c r="P34" s="15" t="inlineStr"/>
-      <c r="Q34" s="15" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34" ht="76" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>manager と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>増減=0</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>既存の manager 権限で見える画面が増減する</t>
         </is>
       </c>
-      <c r="I35" s="13" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J35" s="13" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>全画面（manager でログイン）</t>
         </is>
       </c>
-      <c r="K35" s="13" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L35" s="13" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M35" s="13" t="inlineStr">
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N35" s="15" t="inlineStr"/>
-      <c r="O35" s="15" t="inlineStr"/>
-      <c r="P35" s="15" t="inlineStr"/>
-      <c r="Q35" s="15" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="N34" s="8" t="inlineStr"/>
+      <c r="O34" s="8" t="inlineStr"/>
+      <c r="P34" s="8" t="inlineStr"/>
+      <c r="Q34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35" ht="76" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>shop_manager と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>増減=0</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>既存の shop_manager 権限で見える画面が増減する</t>
         </is>
       </c>
-      <c r="I36" s="13" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>全画面（shop_manager でログイン）</t>
         </is>
       </c>
-      <c r="K36" s="13" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L36" s="13" t="inlineStr">
+      <c r="L35" s="8" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M36" s="13" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N36" s="15" t="inlineStr"/>
-      <c r="O36" s="15" t="inlineStr"/>
-      <c r="P36" s="15" t="inlineStr"/>
-      <c r="Q36" s="15" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36" ht="76" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>F. 事故を防ぐ</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>AC-17</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>自分の権限から権限設定を外せない（自己ロックアウト防止）</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>権限設定を自ロールから外す操作でブロックまたは警告が出る。無警告で保存できる＝0件</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>管理者が自分を締め出し、復旧に開発対応が必要になる</t>
         </is>
       </c>
-      <c r="I37" s="13" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>権限編集の保存時チェック</t>
         </is>
       </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>権限編集</t>
         </is>
       </c>
-      <c r="K37" s="13" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="L37" s="13" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>§9 自己ロックアウト</t>
         </is>
       </c>
-      <c r="M37" s="13" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>T-17.png</t>
         </is>
       </c>
-      <c r="N37" s="15" t="inlineStr"/>
-      <c r="O37" s="15" t="inlineStr"/>
-      <c r="P37" s="15" t="inlineStr"/>
-      <c r="Q37" s="15" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="N36" s="8" t="inlineStr"/>
+      <c r="O36" s="8" t="inlineStr"/>
+      <c r="P36" s="8" t="inlineStr"/>
+      <c r="Q36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37" ht="76" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>F. 事故を防ぐ</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>一般の権限で権限設定ページを開けない</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>店舗ロールで権限設定URL=ブロック</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>一般の権限で権限設定を書き換えられる＝権限機能全体が無意味になる</t>
         </is>
       </c>
-      <c r="I38" s="13" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>権限設定画面の認可</t>
         </is>
       </c>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>権限設定（直URL）</t>
         </is>
       </c>
-      <c r="K38" s="13" t="inlineStr">
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="L38" s="13" t="inlineStr">
+      <c r="L37" s="8" t="inlineStr">
         <is>
           <t>§9</t>
         </is>
       </c>
-      <c r="M38" s="13" t="inlineStr">
+      <c r="M37" s="8" t="inlineStr">
         <is>
           <t>T-17.png</t>
         </is>
       </c>
-      <c r="N38" s="15" t="inlineStr"/>
-      <c r="O38" s="15" t="inlineStr"/>
-      <c r="P38" s="15" t="inlineStr"/>
-      <c r="Q38" s="15" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="N37" s="8" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr"/>
+      <c r="P37" s="8" t="inlineStr"/>
+      <c r="Q37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38" ht="76" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>一覧の許可数が実際の設定と一致する</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>不一致=0件（5ロールで検証）</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>一覧の表示と実際の設定がズレ、確認を誤る</t>
         </is>
       </c>
-      <c r="I39" s="13" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>権限一覧の集計</t>
         </is>
       </c>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="K39" s="13" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="L39" s="13" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>§5.3 権限一覧</t>
         </is>
       </c>
-      <c r="M39" s="13" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>T-05.png</t>
         </is>
       </c>
-      <c r="N39" s="15" t="inlineStr"/>
-      <c r="O39" s="15" t="inlineStr"/>
-      <c r="P39" s="15" t="inlineStr"/>
-      <c r="Q39" s="15" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="N38" s="8" t="inlineStr"/>
+      <c r="O38" s="8" t="inlineStr"/>
+      <c r="P38" s="8" t="inlineStr"/>
+      <c r="Q38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39" ht="76" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>権限編集はどの入口から入っても元の画面に戻る</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>4入口すべてで来た元に戻る（一覧/セルクリック/役割サマリ/割当編集）</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>修正のたびに元の場所へ辿り直すことになり、点検作業が重くなる</t>
         </is>
       </c>
-      <c r="I40" s="13" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>遷移の origin 保持</t>
         </is>
       </c>
-      <c r="J40" s="13" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>権限編集（4入口）</t>
         </is>
       </c>
-      <c r="K40" s="13" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="L40" s="13" t="inlineStr">
+      <c r="L39" s="8" t="inlineStr">
         <is>
           <t>§5.6 F-06〜F-09</t>
         </is>
       </c>
-      <c r="M40" s="13" t="inlineStr">
+      <c r="M39" s="8" t="inlineStr">
         <is>
           <t>T-07.png</t>
         </is>
       </c>
-      <c r="N40" s="15" t="inlineStr"/>
-      <c r="O40" s="15" t="inlineStr"/>
-      <c r="P40" s="15" t="inlineStr"/>
-      <c r="Q40" s="15" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="N39" s="8" t="inlineStr"/>
+      <c r="O39" s="8" t="inlineStr"/>
+      <c r="P39" s="8" t="inlineStr"/>
+      <c r="Q39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40" ht="76" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>役割サマリの割当人数が実態と一致する</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>6権限すべてで 表示N＝実保持者数（差分0）</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>割当人数の表示が実態とズレ、点検の判断を誤る</t>
         </is>
       </c>
-      <c r="I41" s="13" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>役割サマリの集計</t>
         </is>
       </c>
-      <c r="J41" s="13" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>役割サマリ</t>
         </is>
       </c>
-      <c r="K41" s="13" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="L41" s="13" t="inlineStr">
+      <c r="L40" s="8" t="inlineStr">
         <is>
           <t>§5.4 役割サマリ</t>
         </is>
       </c>
-      <c r="M41" s="13" t="inlineStr">
+      <c r="M40" s="8" t="inlineStr">
         <is>
           <t>T-06.png</t>
         </is>
       </c>
-      <c r="N41" s="15" t="inlineStr"/>
-      <c r="O41" s="15" t="inlineStr"/>
-      <c r="P41" s="15" t="inlineStr"/>
-      <c r="Q41" s="15" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="N40" s="8" t="inlineStr"/>
+      <c r="O40" s="8" t="inlineStr"/>
+      <c r="P40" s="8" t="inlineStr"/>
+      <c r="Q40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41" ht="76" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>H. 指標とオーナー</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>指標をまとめて設定でき、他の権限に再利用できる</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>テンプレ適用の結果が定義と一致。保存した組み合わせを他権限で読込できる</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>権限ごとに指標を作り直すことになり運用負荷が高い</t>
         </is>
       </c>
-      <c r="I42" s="13" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート</t>
         </is>
       </c>
-      <c r="J42" s="13" t="inlineStr">
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート</t>
         </is>
       </c>
-      <c r="K42" s="13" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="L42" s="13" t="inlineStr">
+      <c r="L41" s="8" t="inlineStr">
         <is>
           <t>§5.5</t>
         </is>
       </c>
-      <c r="M42" s="13" t="inlineStr">
+      <c r="M41" s="8" t="inlineStr">
         <is>
           <t>T-20.png</t>
         </is>
       </c>
-      <c r="N42" s="15" t="inlineStr"/>
-      <c r="O42" s="15" t="inlineStr"/>
-      <c r="P42" s="15" t="inlineStr"/>
-      <c r="Q42" s="15" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="N41" s="8" t="inlineStr"/>
+      <c r="O41" s="8" t="inlineStr"/>
+      <c r="P41" s="8" t="inlineStr"/>
+      <c r="Q41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42" ht="76" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>H. 指標とオーナー</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="E43" s="19" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>オーナー専用機能が読取専用・オーナー限定である</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>指標管理に編集UI（トグル／コピー／条件設定）が表示される＝0件。オーナー以外が付与先指定を実行できる＝0件</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>全権の設定が誤って変更される</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>オーナー操作</t>
         </is>
       </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>オーナー操作</t>
         </is>
       </c>
-      <c r="K43" s="13" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="L43" s="13" t="inlineStr">
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t>§5.3 オーナー操作</t>
         </is>
       </c>
-      <c r="M43" s="13" t="inlineStr">
+      <c r="M42" s="8" t="inlineStr">
         <is>
           <t>T-20.png</t>
         </is>
       </c>
-      <c r="N43" s="15" t="inlineStr"/>
-      <c r="O43" s="15" t="inlineStr"/>
-      <c r="P43" s="15" t="inlineStr"/>
-      <c r="Q43" s="15" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="N42" s="8" t="inlineStr"/>
+      <c r="O42" s="8" t="inlineStr"/>
+      <c r="P42" s="8" t="inlineStr"/>
+      <c r="Q42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>AC-31</t>
         </is>
       </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>一覧の表示絞り込みが次回も保持される</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>画面を離れて戻ったとき、列選択が離脱前と一致（スコープ別に保持）</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>点検のたびに表示条件を選び直すことになる（利便性）</t>
         </is>
       </c>
-      <c r="I44" s="13" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>localStorage</t>
         </is>
       </c>
-      <c r="J44" s="13" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="K44" s="13" t="inlineStr">
+      <c r="K43" s="8" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="L44" s="13" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr">
         <is>
           <t>§5.3</t>
         </is>
       </c>
-      <c r="M44" s="13" t="inlineStr">
+      <c r="M43" s="8" t="inlineStr">
         <is>
           <t>T-05.png</t>
         </is>
       </c>
-      <c r="N44" s="15" t="inlineStr"/>
-      <c r="O44" s="15" t="inlineStr"/>
-      <c r="P44" s="15" t="inlineStr"/>
-      <c r="Q44" s="15" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="N43" s="8" t="inlineStr"/>
+      <c r="O43" s="8" t="inlineStr"/>
+      <c r="P43" s="8" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44" ht="76" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>K-01</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>権限はロール経由でのみ付与する（人に直接付けない）</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>ユーザー個別に権限内容を編集できるUI・APIが存在しない＝0件</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>人ごとに権限を作り込めてしまい、従業員数だけ設定が増殖して誰が何を見えるか把握できなくなる</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>割当はロールの選択のみ。role_permissions はユーザーに紐付けない</t>
         </is>
       </c>
-      <c r="J45" s="13" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>ユーザー割当／割当編集</t>
         </is>
       </c>
-      <c r="K45" s="13" t="inlineStr">
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L45" s="13" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr">
         <is>
           <t>§7-A 権限はロール経由で与える（人に直接付けない）</t>
         </is>
       </c>
-      <c r="M45" s="13" t="inlineStr">
+      <c r="M44" s="8" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N45" s="15" t="inlineStr"/>
-      <c r="O45" s="15" t="inlineStr"/>
-      <c r="P45" s="15" t="inlineStr"/>
-      <c r="Q45" s="15" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="N44" s="8" t="inlineStr"/>
+      <c r="O44" s="8" t="inlineStr"/>
+      <c r="P44" s="8" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45" ht="76" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>K-02</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>区分とデータ範囲を独立した軸として実装する</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>店舗ロールでも担当店舗を全店・複数店に設定できる＝制約なし</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>「店舗ロール＝自店舗のみ」と固定され、エリアマネージャーや複数店舗所属が表現できない</t>
         </is>
       </c>
-      <c r="I46" s="13" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>user_roles.store_ids は区分と独立。区分でstore_idsを制限しない</t>
         </is>
       </c>
-      <c r="J46" s="13" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>割当編集（対象店舗）</t>
         </is>
       </c>
-      <c r="K46" s="13" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L46" s="13" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr">
         <is>
           <t>§7-C 区分とデータ範囲は独立した別軸</t>
         </is>
       </c>
-      <c r="M46" s="13" t="inlineStr">
+      <c r="M45" s="8" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N46" s="15" t="inlineStr"/>
-      <c r="O46" s="15" t="inlineStr"/>
-      <c r="P46" s="15" t="inlineStr"/>
-      <c r="Q46" s="15" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="N45" s="8" t="inlineStr"/>
+      <c r="O45" s="8" t="inlineStr"/>
+      <c r="P45" s="8" t="inlineStr"/>
+      <c r="Q45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46" ht="76" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>K-03</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>操作は登録・編集・削除を一体で扱う</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>権限の状態が なし／閲覧／操作 の3つ＝4つ目が存在しない</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>4状態に戻ると設定コストが跳ね上がり、顧客が使いこなせない</t>
         </is>
       </c>
-      <c r="I47" s="13" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>role_permissions.level は 0/1/2 のみ。削除専用フラグを作らない</t>
         </is>
       </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>権限編集（権限内容）</t>
         </is>
       </c>
-      <c r="K47" s="13" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L47" s="13" t="inlineStr">
+      <c r="L46" s="8" t="inlineStr">
         <is>
           <t>§7-D 操作＝登録・編集・削除を一体（削除を分けない） / §3.2</t>
         </is>
       </c>
-      <c r="M47" s="13" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N47" s="15" t="inlineStr"/>
-      <c r="O47" s="15" t="inlineStr"/>
-      <c r="P47" s="15" t="inlineStr"/>
-      <c r="Q47" s="15" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="N46" s="8" t="inlineStr"/>
+      <c r="O46" s="8" t="inlineStr"/>
+      <c r="P46" s="8" t="inlineStr"/>
+      <c r="Q46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47" ht="76" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>K-04</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>機密ランクを画面に出さない</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>指標一覧・指標条件設定に機密度のバッジ・ラベルが表示されない＝0件</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>顧客が指標を選ぶたびにランクの妥当性を判断させることになる</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>sens は初期値の算出にのみ使用。UIに描画しない</t>
         </is>
       </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>指標一覧／指標条件設定</t>
         </is>
       </c>
-      <c r="K48" s="13" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L48" s="13" t="inlineStr">
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>§7-E 機密ランクを画面に出さない</t>
         </is>
       </c>
-      <c r="M48" s="13" t="inlineStr">
+      <c r="M47" s="8" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N48" s="15" t="inlineStr"/>
-      <c r="O48" s="15" t="inlineStr"/>
-      <c r="P48" s="15" t="inlineStr"/>
-      <c r="Q48" s="15" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="8" t="inlineStr"/>
+      <c r="P47" s="8" t="inlineStr"/>
+      <c r="Q47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48" ht="76" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>K-05</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>会社指標を店舗ロールに付与できる（禁止しない）</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>店舗ロールの指標一覧で会社指標をONにできる（ハードブロック＝0件）。初期状態のON件数は 従業員=会社0／店長=会社8</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>ハードブロックすると「店長にも全社利益を見せたい」という顧客の運用方針を否定する</t>
         </is>
       </c>
-      <c r="I49" s="13" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>既定OFF＋管理者オプトイン。行スコープ遮断とは独立</t>
         </is>
       </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>指標一覧（会社タブ）</t>
         </is>
       </c>
-      <c r="K49" s="13" t="inlineStr">
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L49" s="13" t="inlineStr">
+      <c r="L48" s="8" t="inlineStr">
         <is>
           <t>§7-F 会社指標を店舗ロールに出すことを禁止しない</t>
         </is>
       </c>
-      <c r="M49" s="13" t="inlineStr">
+      <c r="M48" s="8" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N49" s="15" t="inlineStr"/>
-      <c r="O49" s="15" t="inlineStr"/>
-      <c r="P49" s="15" t="inlineStr"/>
-      <c r="Q49" s="15" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="N48" s="8" t="inlineStr"/>
+      <c r="O48" s="8" t="inlineStr"/>
+      <c r="P48" s="8" t="inlineStr"/>
+      <c r="Q48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49" ht="76" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>K-06</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>「含める」チェックを店舗選択と統合しない</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>一括割当で店舗を選んだだけでは権限が付与されない</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>誤クリックがそのまま権限付与になり、意図しない人に権限が渡る</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>含めるチェックを明示の安全装置として残す</t>
         </is>
       </c>
-      <c r="J50" s="13" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>一括割当</t>
         </is>
       </c>
-      <c r="K50" s="13" t="inlineStr">
+      <c r="K49" s="8" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L50" s="13" t="inlineStr">
+      <c r="L49" s="8" t="inlineStr">
         <is>
           <t>§7-G 「含める」チェックを店舗選択と統合しない</t>
         </is>
       </c>
-      <c r="M50" s="13" t="inlineStr">
+      <c r="M49" s="8" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr"/>
-      <c r="O50" s="15" t="inlineStr"/>
-      <c r="P50" s="15" t="inlineStr"/>
-      <c r="Q50" s="15" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="N49" s="8" t="inlineStr"/>
+      <c r="O49" s="8" t="inlineStr"/>
+      <c r="P49" s="8" t="inlineStr"/>
+      <c r="Q49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50" ht="76" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>M7 境界設計が守られている</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>動作テストで見えない設計の約束が実装で守られている</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>K. 境界設計を守る（動作テストでは検出できない）</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>K-07</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>MVP必須</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>画面カテゴリを新しく追加したとき、既存のすべての権限で既定を「なし」にする</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>新カテゴリ追加時に自動で許可される権限が0件。既存権限の許可数が追加前後で変わらない</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>画面が増えるたびに全員が黙って見られるようになる。顧客は増えたことに気づけず、閲覧範囲が意図せず広がる</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>含めるチェックを明示の安全装置として残す</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>権限一覧（追加前後の許可数）／コード上の既定値</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>T-24</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>§7 境界設計（既定は安全側）。※仕様§1では新カテゴリの追加UI自体はP1対象外とされているが、追加された際の既定値は設計の約束として必要</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>エンジニアとの棚卸し記録（既定値のコード箇所）</t>
+        </is>
+      </c>
+      <c r="N50" s="8" t="inlineStr"/>
+      <c r="O50" s="8" t="inlineStr"/>
+      <c r="P50" s="8" t="inlineStr"/>
+      <c r="Q50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51" ht="76" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>M8 顧客価値に到達</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>I. 顧客価値に到達しているか</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>画面単位で表現できる4シナリオの権限が作れる</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>SC-01a経理（会社）／SC-01b経理（店舗）／SC-02人事／SC-04バイトL／SC-06スタッフ の5件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>顧客が求める権限を作れない＝リリースする意味がない</t>
         </is>
       </c>
-      <c r="I51" s="13" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>（総合判定）</t>
         </is>
       </c>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>全画面（6シナリオ）</t>
         </is>
       </c>
-      <c r="K51" s="13" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>T-22</t>
         </is>
       </c>
-      <c r="L51" s="13" t="inlineStr">
+      <c r="L51" s="8" t="inlineStr">
         <is>
           <t>§1.2 顧客要望</t>
         </is>
       </c>
-      <c r="M51" s="13" t="inlineStr">
+      <c r="M51" s="8" t="inlineStr">
         <is>
           <t>6シナリオの判定表</t>
         </is>
       </c>
-      <c r="N51" s="15" t="inlineStr"/>
-      <c r="O51" s="15" t="inlineStr"/>
-      <c r="P51" s="15" t="inlineStr"/>
-      <c r="Q51" s="15" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="N51" s="8" t="inlineStr"/>
+      <c r="O51" s="8" t="inlineStr"/>
+      <c r="P51" s="8" t="inlineStr"/>
+      <c r="Q51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52" ht="76" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>担当外店舗のデータを返さない</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>他店データ=0件。2店舗合計=表示合計</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>担当外店舗のデータが混ざる。P3（データ範囲の強制）の要否判断に使う</t>
         </is>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>P3 行スコープ強制</t>
         </is>
       </c>
-      <c r="J52" s="13" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>集計／売上分析</t>
         </is>
       </c>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>T-11 T-23</t>
         </is>
       </c>
-      <c r="L52" s="13" t="inlineStr">
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>§3.1 ④ / §8-6</t>
         </is>
       </c>
-      <c r="M52" s="13" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>T-11.png</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr"/>
-      <c r="O52" s="15" t="inlineStr"/>
-      <c r="P52" s="15" t="inlineStr"/>
-      <c r="Q52" s="15" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="N52" s="8" t="inlineStr"/>
+      <c r="O52" s="8" t="inlineStr"/>
+      <c r="P52" s="8" t="inlineStr"/>
+      <c r="Q52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53" ht="76" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>AC-24</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>閲覧のみの権限で更新できない</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>保存・登録・削除=不可（値が変わらない）</t>
         </is>
       </c>
-      <c r="H53" s="13" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>閲覧のみの権限で更新できてしまう。P2の要否判断に使う</t>
         </is>
       </c>
-      <c r="I53" s="13" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>P2 操作判定</t>
         </is>
       </c>
-      <c r="J53" s="13" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>費用設定／従業員管理</t>
         </is>
       </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="L53" s="13" t="inlineStr">
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>§3.1 ② / §8-6</t>
         </is>
       </c>
-      <c r="M53" s="13" t="inlineStr">
+      <c r="M53" s="8" t="inlineStr">
         <is>
           <t>T-23.png</t>
         </is>
       </c>
-      <c r="N53" s="15" t="inlineStr"/>
-      <c r="O53" s="15" t="inlineStr"/>
-      <c r="P53" s="15" t="inlineStr"/>
-      <c r="Q53" s="15" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="N53" s="8" t="inlineStr"/>
+      <c r="O53" s="8" t="inlineStr"/>
+      <c r="P53" s="8" t="inlineStr"/>
+      <c r="Q53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54" ht="76" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>許可していない指標を表示しない</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>ダッシュボード・分析画面に非許可指標=0件</t>
         </is>
       </c>
-      <c r="H54" s="13" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>許可外の指標が表示される。P4の要否判断に使う</t>
         </is>
       </c>
-      <c r="I54" s="13" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>P4 指標可視性</t>
         </is>
       </c>
-      <c r="J54" s="13" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>ダッシュボード／分析画面</t>
         </is>
       </c>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>T-19 T-23</t>
         </is>
       </c>
-      <c r="L54" s="13" t="inlineStr">
+      <c r="L54" s="8" t="inlineStr">
         <is>
           <t>§3.1 ③ / §5.5</t>
         </is>
       </c>
-      <c r="M54" s="13" t="inlineStr">
+      <c r="M54" s="8" t="inlineStr">
         <is>
           <t>T-19.png</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr"/>
-      <c r="O54" s="15" t="inlineStr"/>
-      <c r="P54" s="15" t="inlineStr"/>
-      <c r="Q54" s="15" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="N54" s="8" t="inlineStr"/>
+      <c r="O54" s="8" t="inlineStr"/>
+      <c r="P54" s="8" t="inlineStr"/>
+      <c r="Q54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55" ht="76" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>AC-26</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>変更が監査ログに残る</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>権限の作成・割当の変更が操作ログに記録される＝記録漏れ0件（P1では実測を記録するのみ）</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>変更履歴が残らない。P5の要否判断に使う</t>
         </is>
       </c>
-      <c r="I55" s="13" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>P5 audit_logs</t>
         </is>
       </c>
-      <c r="J55" s="13" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>（管理画面のログ）</t>
         </is>
       </c>
-      <c r="K55" s="13" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="L55" s="13" t="inlineStr">
+      <c r="L55" s="8" t="inlineStr">
         <is>
           <t>§6 audit_logs</t>
         </is>
       </c>
-      <c r="M55" s="13" t="inlineStr">
+      <c r="M55" s="8" t="inlineStr">
         <is>
           <t>T-23.png</t>
         </is>
       </c>
-      <c r="N55" s="15" t="inlineStr"/>
-      <c r="O55" s="15" t="inlineStr"/>
-      <c r="P55" s="15" t="inlineStr"/>
-      <c r="Q55" s="15" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="N55" s="8" t="inlineStr"/>
+      <c r="O55" s="8" t="inlineStr"/>
+      <c r="P55" s="8" t="inlineStr"/>
+      <c r="Q55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56" ht="76" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>AC-32</t>
         </is>
       </c>
-      <c r="E56" s="21" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>データ範囲・操作を要する権限が作れる</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>データ範囲・操作を要する権限が作れない。P2/P3の前倒し判断に使う</t>
         </is>
       </c>
-      <c r="I56" s="13" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>P2／P3</t>
         </is>
       </c>
-      <c r="J56" s="13" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>全画面（SC-03／SC-05）</t>
         </is>
       </c>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>T-22 T-23</t>
         </is>
       </c>
-      <c r="L56" s="13" t="inlineStr">
+      <c r="L56" s="8" t="inlineStr">
         <is>
           <t>§1.2 顧客要望 / §8-6</t>
         </is>
       </c>
-      <c r="M56" s="13" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>T-22.png</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr"/>
-      <c r="O56" s="15" t="inlineStr"/>
-      <c r="P56" s="15" t="inlineStr"/>
-      <c r="Q56" s="15" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="N56" s="8" t="inlineStr"/>
+      <c r="O56" s="8" t="inlineStr"/>
+      <c r="P56" s="8" t="inlineStr"/>
+      <c r="Q56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57" ht="76" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
-      <c r="E57" s="21" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>会社画面と店舗画面の両方を扱う権限が作れる</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>1人の権限で 会社画面（お支払い等）と店舗画面（費用設定等）の両方が開ける＝現状は×が想定</t>
         </is>
       </c>
-      <c r="H57" s="13" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>経理のように会社の支払と店舗の費用設定を両方見る職務が、1人1ロールでは表現できず権限を2つ作って人を分ける運用になる</t>
         </is>
       </c>
-      <c r="I57" s="13" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>user_roles（1人1ロール）／区分の設計</t>
         </is>
       </c>
-      <c r="J57" s="13" t="inlineStr">
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>権限編集（区分）</t>
         </is>
       </c>
-      <c r="K57" s="13" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>T-09 T-09b</t>
         </is>
       </c>
-      <c r="L57" s="13" t="inlineStr">
+      <c r="L57" s="8" t="inlineStr">
         <is>
           <t>§3.5 / §7-C 区分とデータ範囲は独立した別軸</t>
         </is>
       </c>
-      <c r="M57" s="13" t="inlineStr">
+      <c r="M57" s="8" t="inlineStr">
         <is>
           <t>T-09b.png</t>
         </is>
       </c>
-      <c r="N57" s="15" t="inlineStr"/>
-      <c r="O57" s="15" t="inlineStr"/>
-      <c r="P57" s="15" t="inlineStr"/>
-      <c r="Q57" s="15" t="inlineStr"/>
+      <c r="N57" s="8" t="inlineStr"/>
+      <c r="O57" s="8" t="inlineStr"/>
+      <c r="P57" s="8" t="inlineStr"/>
+      <c r="Q57" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:Q57"/>
-  <mergeCells count="10">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B6:D6"/>
-  </mergeCells>
-  <conditionalFormatting sqref="N18:N57">
+  <conditionalFormatting sqref="N17:N57">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"NG"</formula>
+      <formula>"OK"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J13">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"完了"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>LEFT(J5,2)="未達"</formula>
+      <formula>"NG"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N18:N57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N17:N57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -571,15 +571,15 @@
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5">
-        <f>COUNTIF($A$17:$A$57,A5)</f>
+        <f>COUNTIF($A$17:$A$56,A5)</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS($A$17:$A$57,A5,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A5,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>COUNTIFS($A$17:$A$57,A5,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A5,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="5">
@@ -605,15 +605,15 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5">
-        <f>COUNTIF($A$17:$A$57,A6)</f>
+        <f>COUNTIF($A$17:$A$56,A6)</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS($A$17:$A$57,A6,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A6,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>COUNTIFS($A$17:$A$57,A6,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A6,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="5">
@@ -639,15 +639,15 @@
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5">
-        <f>COUNTIF($A$17:$A$57,A7)</f>
+        <f>COUNTIF($A$17:$A$56,A7)</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS($A$17:$A$57,A7,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A7,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>COUNTIFS($A$17:$A$57,A7,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A7,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="5">
@@ -673,15 +673,15 @@
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5">
-        <f>COUNTIF($A$17:$A$57,A8)</f>
+        <f>COUNTIF($A$17:$A$56,A8)</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS($A$17:$A$57,A8,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A8,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>COUNTIFS($A$17:$A$57,A8,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A8,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="5">
@@ -707,15 +707,15 @@
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5">
-        <f>COUNTIF($A$17:$A$57,A9)</f>
+        <f>COUNTIF($A$17:$A$56,A9)</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS($A$17:$A$57,A9,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A9,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>COUNTIFS($A$17:$A$57,A9,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A9,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="5">
@@ -741,15 +741,15 @@
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5">
-        <f>COUNTIF($A$17:$A$57,A10)</f>
+        <f>COUNTIF($A$17:$A$56,A10)</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS($A$17:$A$57,A10,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A10,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>COUNTIFS($A$17:$A$57,A10,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A10,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="5">
@@ -775,15 +775,15 @@
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5">
-        <f>COUNTIF($A$17:$A$57,A11)</f>
+        <f>COUNTIF($A$17:$A$56,A11)</f>
         <v/>
       </c>
       <c r="F11" s="5">
-        <f>COUNTIFS($A$17:$A$57,A11,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A11,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>COUNTIFS($A$17:$A$57,A11,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A11,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H11" s="5">
@@ -809,15 +809,15 @@
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5">
-        <f>COUNTIF($A$17:$A$57,A12)</f>
+        <f>COUNTIF($A$17:$A$56,A12)</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS($A$17:$A$57,A12,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A12,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>COUNTIFS($A$17:$A$57,A12,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A12,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H12" s="5">
@@ -843,15 +843,15 @@
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5">
-        <f>COUNTIF($A$17:$A$57,A13)</f>
+        <f>COUNTIF($A$17:$A$56,A13)</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS($A$17:$A$57,A13,$N$17:$N$57,"OK")</f>
+        <f>COUNTIFS($A$17:$A$56,A13,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>COUNTIFS($A$17:$A$57,A13,$N$17:$N$57,"NG")</f>
+        <f>COUNTIFS($A$17:$A$56,A13,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
       <c r="H13" s="5">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>新規追加した画面が全ロールで「なし」＝例外0件</t>
+          <t>新規追加した画面が全ロールで「なし」＝例外0件。**コード上の既定値も T-24 の棚卸しで確認する**</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>今後追加される画面が全権限に開いた状態で出る</t>
+          <t>画面が増えるたびに全員が黙って見られるようになる。顧客は増えたことに気づけず、閲覧範囲が意図せず広がる</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-02 T-24</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>メニュー非表示かつ直URLでも開けない=100%</t>
+          <t>メニュー非表示かつ直URLでも開けない=100%。**ダッシュボードは閲覧固定（権限設定の対象外）のため除く**</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>全項目オフのロールでログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ0件</t>
+          <t>全項目オフのロールでログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ0件。**ダッシュボードは閲覧固定で「なし」に設定できない前提**</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>不一致=0件（5ロールで検証）</t>
+          <t>不一致=0件（dataset/08 の**7権限すべて**）</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>6権限すべてで 表示N＝実保持者数（差分0）</t>
+          <t>**7権限すべてで** 表示N＝実保持者数（差分0）</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>店舗ロールでも担当店舗を全店・複数店に設定できる＝制約なし</t>
+          <t>店舗ロールでも担当店舗を全店・複数店に設定できる＝**上限の制約がない**。※下限は AC-19 のとおり1件以上が必須（0件は保存不可）</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -3296,22 +3296,22 @@
     <row r="50" ht="76" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>M7 境界設計が守られている</t>
+          <t>M8 顧客価値に到達</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>動作テストで見えない設計の約束が実装で守られている</t>
+          <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>K. 境界設計を守る（動作テストでは検出できない）</t>
+          <t>I. 顧客価値に到達しているか</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>K-07</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>画面カテゴリを新しく追加したとき、既存のすべての権限で既定を「なし」にする</t>
+          <t>画面単位で表現できる4シナリオの権限が作れる</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>新カテゴリ追加時に自動で許可される権限が0件。既存権限の許可数が追加前後で変わらない</t>
+          <t>SC-01a経理（会社）／SC-01b経理（店舗）／SC-02人事／SC-04バイトL／SC-06スタッフ の5件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>画面が増えるたびに全員が黙って見られるようになる。顧客は増えたことに気づけず、閲覧範囲が意図せず広がる</t>
+          <t>顧客が求める権限を作れない＝リリースする意味がない</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>含めるチェックを明示の安全装置として残す</t>
+          <t>（総合判定）</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>権限一覧（追加前後の許可数）／コード上の既定値</t>
+          <t>全画面（6シナリオ）</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>§7 境界設計（既定は安全側）。※仕様§1では新カテゴリの追加UI自体はP1対象外とされているが、追加された際の既定値は設計の約束として必要</t>
+          <t>§1.2 顧客要望</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>エンジニアとの棚卸し記録（既定値のコード箇所）</t>
+          <t>6シナリオの判定表</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr"/>
@@ -3367,67 +3367,67 @@
     <row r="51" ht="76" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>M8 顧客価値に到達</t>
+          <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
+          <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>I. 顧客価値に到達しているか</t>
+          <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>MVP必須</t>
+          <t>次段階</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>画面単位で表現できる4シナリオの権限が作れる</t>
+          <t>担当外店舗のデータを返さない</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>SC-01a経理（会社）／SC-01b経理（店舗）／SC-02人事／SC-04バイトL／SC-06スタッフ の5件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
+          <t>他店データ=0件。2店舗合計=表示合計</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>顧客が求める権限を作れない＝リリースする意味がない</t>
+          <t>担当外店舗のデータが混ざる。P3（データ範囲の強制）の要否判断に使う</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>（総合判定）</t>
+          <t>P3 行スコープ強制</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>全画面（6シナリオ）</t>
+          <t>集計／売上分析</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-11 T-23</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>§1.2 顧客要望</t>
+          <t>§3.1 ④ / §8-6</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>6シナリオの判定表</t>
+          <t>T-11.png</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-24</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -3463,42 +3463,42 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>担当外店舗のデータを返さない</t>
+          <t>閲覧のみの権限で更新できない</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>他店データ=0件。2店舗合計=表示合計</t>
+          <t>保存・登録・削除=不可（値が変わらない）</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>担当外店舗のデータが混ざる。P3（データ範囲の強制）の要否判断に使う</t>
+          <t>閲覧のみの権限で更新できてしまう。P2の要否判断に使う</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>P3 行スコープ強制</t>
+          <t>P2 操作判定</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>集計／売上分析</t>
+          <t>費用設定／従業員管理</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>T-11 T-23</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>§3.1 ④ / §8-6</t>
+          <t>§3.1 ② / §8-6</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>T-11.png</t>
+          <t>T-23.png</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr"/>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>AC-24</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -3534,42 +3534,42 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>閲覧のみの権限で更新できない</t>
+          <t>許可していない指標を表示しない</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>保存・登録・削除=不可（値が変わらない）</t>
+          <t>ダッシュボード・分析画面に非許可指標=0件</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>閲覧のみの権限で更新できてしまう。P2の要否判断に使う</t>
+          <t>許可外の指標が表示される。P4の要否判断に使う</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>P2 操作判定</t>
+          <t>P4 指標可視性</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>費用設定／従業員管理</t>
+          <t>ダッシュボード／分析画面</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-19 T-23</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>§3.1 ② / §8-6</t>
+          <t>§3.1 ③ / §5.5</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
-          <t>T-23.png</t>
+          <t>T-19.png</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr"/>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-26</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -3605,42 +3605,42 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>許可していない指標を表示しない</t>
+          <t>変更が監査ログに残る</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>ダッシュボード・分析画面に非許可指標=0件</t>
+          <t>権限の作成・割当の変更が操作ログに記録される＝記録漏れ0件（P1では実測を記録するのみ）</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>許可外の指標が表示される。P4の要否判断に使う</t>
+          <t>変更履歴が残らない。P5の要否判断に使う</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>P4 指標可視性</t>
+          <t>P5 audit_logs</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>ダッシュボード／分析画面</t>
+          <t>（管理画面のログ）</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>T-19 T-23</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>§3.1 ③ / §5.5</t>
+          <t>§6 audit_logs</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
-          <t>T-19.png</t>
+          <t>T-23.png</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr"/>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>AC-26</t>
+          <t>AC-32</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -3676,42 +3676,42 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>変更が監査ログに残る</t>
+          <t>データ範囲・操作を要する権限が作れる</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>権限の作成・割当の変更が操作ログに記録される＝記録漏れ0件（P1では実測を記録するのみ）</t>
+          <t>SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>変更履歴が残らない。P5の要否判断に使う</t>
+          <t>データ範囲・操作を要する権限が作れない。P2/P3の前倒し判断に使う</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>P5 audit_logs</t>
+          <t>P2／P3</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>（管理画面のログ）</t>
+          <t>全画面（SC-03／SC-05）</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-22 T-23</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>§6 audit_logs</t>
+          <t>§1.2 顧客要望 / §8-6</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
-          <t>T-23.png</t>
+          <t>T-22.png</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr"/>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>AC-32</t>
+          <t>AC-34</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -3747,42 +3747,42 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>データ範囲・操作を要する権限が作れる</t>
+          <t>会社画面と店舗画面の両方を扱う権限が作れる</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）</t>
+          <t>1人の権限で 会社画面（お支払い等）と店舗画面（費用設定等）の両方が開ける＝現状は×が想定</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>データ範囲・操作を要する権限が作れない。P2/P3の前倒し判断に使う</t>
+          <t>経理のように会社の支払と店舗の費用設定を両方見る職務が、1人1ロールでは表現できず権限を2つ作って人を分ける運用になる</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>P2／P3</t>
+          <t>user_roles（1人1ロール）／区分の設計</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>全画面（SC-03／SC-05）</t>
+          <t>権限編集（区分）</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>T-22 T-23</t>
+          <t>T-09 T-09b</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>§1.2 顧客要望 / §8-6</t>
+          <t>§3.5 / §7-C 区分とデータ範囲は独立した別軸</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
-          <t>T-22.png</t>
+          <t>T-09b.png</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr"/>
@@ -3790,79 +3790,8 @@
       <c r="P56" s="8" t="inlineStr"/>
       <c r="Q56" s="8" t="inlineStr"/>
     </row>
-    <row r="57" ht="76" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>M9 次段階（P1対象外）</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>J. 次段階（P1では実装しない）</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>AC-34</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>次段階</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>会社画面と店舗画面の両方を扱う権限が作れる</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>1人の権限で 会社画面（お支払い等）と店舗画面（費用設定等）の両方が開ける＝現状は×が想定</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>経理のように会社の支払と店舗の費用設定を両方見る職務が、1人1ロールでは表現できず権限を2つ作って人を分ける運用になる</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>user_roles（1人1ロール）／区分の設計</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>権限編集（区分）</t>
-        </is>
-      </c>
-      <c r="K57" s="8" t="inlineStr">
-        <is>
-          <t>T-09 T-09b</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>§3.5 / §7-C 区分とデータ範囲は独立した別軸</t>
-        </is>
-      </c>
-      <c r="M57" s="8" t="inlineStr">
-        <is>
-          <t>T-09b.png</t>
-        </is>
-      </c>
-      <c r="N57" s="8" t="inlineStr"/>
-      <c r="O57" s="8" t="inlineStr"/>
-      <c r="P57" s="8" t="inlineStr"/>
-      <c r="Q57" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="N17:N57">
+  <conditionalFormatting sqref="N17:N56">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3871,7 +3800,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N17:N57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N17:N56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>ベース選択に4種（オーナー相当/本部管理/店長/従業員）＋プレーンが出る。エリア長は含まれない</t>
+          <t>ベース選択に4種（オーナー相当/本部管理/店長/従業員）＋**まっさら（なし）**が出る。エリア長は含まれない</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>プレーン選択時に許可=0件</t>
+          <t>**まっさら（なし）**を選んだとき許可=0件</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>権限編集（プレーン）</t>
+          <t>権限編集（まっさら（なし））</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>権限編集（プレーン選択時）</t>
+          <t>権限編集（まっさら（なし）選択時）</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）</t>
+          <t>**次段階の到達目標**。SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）。**P1では×が想定され、×であること自体が P2（操作制限）・P3（データ範囲）を前倒しする根拠になる**。P1では判定せず結果を記録する</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="列仕様" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,22 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +65,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F7A8C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF3F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,10 +99,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -94,12 +123,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,3316 +505,4119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>権限設定 受入条件表 ─ どこまで実装できれば合格か</t>
+          <t>受入条件表 列仕様</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「合否」に OK / NG を入れると下の到達状況が自動で集計されます。判定は上のマイルストーン順に進めてください。</t>
+          <t>どこまで実装できれば合格かを定めた表です。実装が条件を満たしているかを確かめ、「合否」を埋めます。実際の画面で動かして確かめる手順は 20260804_権限設定_02_検証プラン.xlsx です。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>列名</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>何を書くか</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>記入者</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>例</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>M1〜M9。実装の順番。上から順に到達させる</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>M2 制御が効く</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>マイルストーンの完了条件</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>そのマイルストーンが終わったと言える状態</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>設計ポイント</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A〜K。同じ観点の条件をまとめたもの。定義は 00_定義表.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>D. 制御が実際に効く</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>条件ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>AC＝機能の条件、K＝境界設計（動作テストでは検出できない）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>AC-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>実装レベル</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>MVP必須／品質必須／推奨／次段階。次段階はP1では実装しない</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>MVP必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>何を実装するか</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>実装すべきことを一文で</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>許可していない画面が開けない。メニュー非表示だけでなく直URLも塞ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>合格ライン（この数値を満たせば実装完了）</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>OK/NGを分ける数値の線。件数・割合で書く</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>メニュー非表示かつ直URLでも開けない=100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>実装できていないと起きること</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>満たさないまま出すと何が起きるか。優先順位の判断材料</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>メニューから消しても直URLで開けてしまい、権限を絞った意味がなくなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>実装箇所</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>どこに実装されるか。エンジニアとの確認用</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ルーティング／各画面のガード</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>確認する画面</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>実装できているかを確かめる画面</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>各画面（メニューと直URL）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>対応検証ID</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>この条件を確かめる検証ケース。検証プランの検証IDと対応</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>T-09 T-09b T-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページの該当箇所</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>顧客に何と説明しているか。NGならヘルプの記述も直す必要がある</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の根拠</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>仕様書のどの節に基づくか</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>§4 段階導入 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>エビデンス</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>合否の根拠として残すもの。スクショ名や記録</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>T-09.png T-09b.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>合否</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>OK／NG／対象外。入れると上のマイルストーン集計に反映される</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>実測値</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>確かめた結果の数値・状態をそのまま書く</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>開ける5画面／開けない3画面とも100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>判定者</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>誰が判定したか</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>鈴木</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>判定日</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>いつ判定したか。実装が変わると結果も変わるため必須</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>■ 使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>1. マイルストーン M1 から順に、その条件が実装されているかをエンジニアと確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2. 「確認する画面」を開き、「合格ライン」の数値を満たしているかを見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>3. 「実測値」「合否」「判定者」「判定日」を記入する。「エビデンス」に根拠を残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>4. 上の集計ブロックでマイルストーンごとの到達率が自動計算される</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>5. NG のときは「対応検証ID」で挙動を確かめ、「ヘルプページの該当箇所」で顧客への説明も直す必要があるかを見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>※ 実装の確認がこの表、実際に動かしての確認が検証プラン。役割が違うので両方を使う</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>権限設定 受入条件表 ─ どこまで実装できれば合格か</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>「合否」に OK / NG を入れると下の到達状況が自動で集計されます。判定は上のマイルストーン順に進めてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>マイルストーン</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>条件数</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>未判定</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>到達率</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5">
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10">
         <f>COUNTIF($A$17:$A$56,A5)</f>
         <v/>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="10">
         <f>COUNTIFS($A$17:$A$56,A5,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="10">
         <f>COUNTIFS($A$17:$A$56,A5,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="10">
         <f>E5-F5-G5</f>
         <v/>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="11">
         <f>IF(E5=0,"",F5/E5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10">
         <f>COUNTIF($A$17:$A$56,A6)</f>
         <v/>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="10">
         <f>COUNTIFS($A$17:$A$56,A6,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="10">
         <f>COUNTIFS($A$17:$A$56,A6,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="10">
         <f>E6-F6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="11">
         <f>IF(E6=0,"",F6/E6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5">
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10">
         <f>COUNTIF($A$17:$A$56,A7)</f>
         <v/>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="10">
         <f>COUNTIFS($A$17:$A$56,A7,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="10">
         <f>COUNTIFS($A$17:$A$56,A7,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="10">
         <f>E7-F7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="11">
         <f>IF(E7=0,"",F7/E7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5">
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10">
         <f>COUNTIF($A$17:$A$56,A8)</f>
         <v/>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="10">
         <f>COUNTIFS($A$17:$A$56,A8,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="10">
         <f>COUNTIFS($A$17:$A$56,A8,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="10">
         <f>E8-F8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="11">
         <f>IF(E8=0,"",F8/E8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5">
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10">
         <f>COUNTIF($A$17:$A$56,A9)</f>
         <v/>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="10">
         <f>COUNTIFS($A$17:$A$56,A9,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="10">
         <f>COUNTIFS($A$17:$A$56,A9,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="10">
         <f>E9-F9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="11">
         <f>IF(E9=0,"",F9/E9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5">
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10">
         <f>COUNTIF($A$17:$A$56,A10)</f>
         <v/>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="10">
         <f>COUNTIFS($A$17:$A$56,A10,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="10">
         <f>COUNTIFS($A$17:$A$56,A10,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="10">
         <f>E10-F10-G10</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="11">
         <f>IF(E10=0,"",F10/E10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5">
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10">
         <f>COUNTIF($A$17:$A$56,A11)</f>
         <v/>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="10">
         <f>COUNTIFS($A$17:$A$56,A11,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="10">
         <f>COUNTIFS($A$17:$A$56,A11,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="10">
         <f>E11-F11-G11</f>
         <v/>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="11">
         <f>IF(E11=0,"",F11/E11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>M8 顧客価値に到達</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5">
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="10">
         <f>COUNTIF($A$17:$A$56,A12)</f>
         <v/>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="10">
         <f>COUNTIFS($A$17:$A$56,A12,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="10">
         <f>COUNTIFS($A$17:$A$56,A12,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="10">
         <f>E12-F12-G12</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="11">
         <f>IF(E12=0,"",F12/E12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5">
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10">
         <f>COUNTIF($A$17:$A$56,A13)</f>
         <v/>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="10">
         <f>COUNTIFS($A$17:$A$56,A13,$N$17:$N$56,"OK")</f>
         <v/>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="10">
         <f>COUNTIFS($A$17:$A$56,A13,$N$17:$N$56,"NG")</f>
         <v/>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="10">
         <f>E13-F13-G13</f>
         <v/>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="11">
         <f>IF(E13=0,"",F13/E13)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>マイルストーンの完了条件</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>設計ポイント</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>条件ID</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>実装レベル</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>何を実装するか</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>合格ライン（この数値を満たせば実装完了）</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>実装できていないと起きること</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>実装箇所</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>確認する画面</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>対応検証ID</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>ヘルプページの該当箇所</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>仕様書の根拠</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>エビデンス</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>実測値</t>
         </is>
       </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>判定者</t>
         </is>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>会社／店舗の区分で、設定対象の画面を出し分ける</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリが設定対象に出る</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>会社用・店舗用の権限を別々に作れない。機能の前提が崩れる</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>権限編集（区分の選択→権限内容）</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>権限編集（区分の切替）</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>§3.3 カテゴリ構成</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>T-03.png</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="8" t="inlineStr"/>
-      <c r="P17" s="8" t="inlineStr"/>
-      <c r="Q17" s="8" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>区分に該当しない画面を設定対象に出さない</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>会社で店舗専用6が出ない、店舗で会社専用4が出ない</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>会社の権限に店舗専用画面が出るなど、設定時に誤った選択肢を選べてしまう</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>権限編集（カテゴリの ctx 判定）</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>権限編集（権限内容）</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>§3.3</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>T-03.png</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="8" t="inlineStr"/>
-      <c r="P18" s="8" t="inlineStr"/>
-      <c r="Q18" s="8" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>権限の作成・保存・再表示が往復して壊れない</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>保存→再表示で欠落・反転=0件</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>設定した権限が保存されない。機能として成立しない</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>権限編集／roles・role_permissions</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>権限編集（保存→再表示）</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>§5.2 権限編集</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="8" t="inlineStr"/>
-      <c r="Q19" s="8" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="76" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>AC-08</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>雛形（ベース）から差分で作れる。移植プリセットを候補に出す</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>ベース選択に4種（オーナー相当/本部管理/店長/従業員）＋**まっさら（なし）**が出る。エリア長は含まれない</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>27画面をゼロから設定することになり、実運用が回らない</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>権限編集①ベース選択</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>権限編集（＋権限を新規作成）</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 2　雛形を選ぶ／STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>§5.2 / §7-H' エリア長を既定テンプレートにしない（2026-08-04）</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>T-01.png</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="8" t="inlineStr"/>
-      <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="8" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>AC-09</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>ゼロから作る場合は全項目オフで始まる</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>**まっさら（なし）**を選んだとき許可=0件</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>意図せず開いた状態の権限ができる</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>権限編集（まっさら（なし））</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>権限編集（まっさら（なし）選択時）</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 2（まっさら（なし））／よくあるご質問（新しい画面が追加された場合）</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>§5.2</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>T-02.png</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr"/>
-      <c r="Q21" s="8" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>A. 権限の単位と範囲</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>AC-12</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>権限が未定義の画面は既定で塞ぐ（fail-closed）</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>新規追加した画面が全ロールで「なし」＝例外0件。**コード上の既定値も T-24 の棚卸しで確認する**</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>画面が増えるたびに全員が黙って見られるようになる。顧客は増えたことに気づけず、閲覧範囲が意図せず広がる</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>判定層の既定値</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>権限編集</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>T-02 T-24</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（新しい画面が追加された場合、権限はどうなりますか）</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>§9 fail-closed</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>T-02.png</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr"/>
-      <c r="O22" s="8" t="inlineStr"/>
-      <c r="P22" s="8" t="inlineStr"/>
-      <c r="Q22" s="8" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>M1 権限が作れる</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>顧客が自分で権限を作り、保存して再表示できる</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>B. 権限をつくる</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>導入時に推奨権限をまとめて登録できる（下書きの保存・破棄を含む）</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>権限テンプレートの適用で推奨4権限が権限一覧に登録される＝4件。一時保存→再訪で選択状態が一致、破棄で既定に戻る</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>導入時に権限を用意できず、導入作業そのものが始められない</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>権限テンプレート画面</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>権限テンプレート</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>§5.6 F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>T-04.png</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="8" t="inlineStr"/>
-      <c r="P23" s="8" t="inlineStr"/>
-      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="76" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>許可した画面が開ける</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>見えるべき画面=100%開ける</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>必要な画面が開けず現場の業務が止まる</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>各画面の表示判定</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>全画面（各権限でログイン）</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>T-09〜T-14</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（アルバイトリーダーに、一部の画面だけ見せたい）／ケース別のやり方（人事担当に、従業員情報だけ見せたい）／ケース別のやり方（新しく入った方には、まず最小限から始めたい）／よくあるご質問（権限を絞りすぎて、何も見えなくなりませんか）／ケース別のやり方（経理担当に、売上とお支払だけ見せたい ＋ 会社と店舗の両方の画面を使わせたい）／ケース別のやり方（経理担当に、売上とお支払だけ見せたい）／ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）／権限を作成する STEP 4（「閲覧」と「操作」は、今回のリリースではどちらも）</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>§3.1 ①画面</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>T-09.png</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="8" t="inlineStr"/>
-      <c r="P24" s="8" t="inlineStr"/>
-      <c r="Q24" s="8" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>許可していない画面が開けない。メニュー非表示だけでなく直URLも塞ぐ</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>メニュー非表示かつ直URLでも開けない=100%。**ダッシュボードは閲覧固定（権限設定の対象外）のため除く**</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>見せてはいけない画面が見える＝情報漏洩</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>コントローラの認可（メニュー生成だけでは不可）</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>全画面（直URLを含む）</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>T-09〜T-14</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（アルバイトリーダーに、一部の画面だけ見せたい）／ケース別のやり方（人事担当に、従業員情報だけ見せたい）／ケース別のやり方（新しく入った方には、まず最小限から始めたい）／よくあるご質問（権限を絞りすぎて、何も見えなくなりませんか）／ケース別のやり方（経理担当に、売上とお支払だけ見せたい ＋ 会社と店舗の両方の画面を使わせたい）／ケース別のやり方（経理担当に、売上とお支払だけ見せたい）／ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）／権限を作成する STEP 4（「閲覧」と「操作」は、今回のリリースではどちらも）</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>§9 誤って通す</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>T-09.png</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr"/>
-      <c r="P25" s="8" t="inlineStr"/>
-      <c r="Q25" s="8" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
+      <c r="Q25" s="4" t="inlineStr"/>
+      <c r="R25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="76" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>権限を最小にしてもログインでき、ランディングに着地する</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>全項目オフのロールでログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ0件。**ダッシュボードは閲覧固定で「なし」に設定できない前提**</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>権限を絞ると使えなくなる＝絞る運用そのものができない</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>ダッシュボード＝閲覧固定</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>ダッシュボード</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（新しく入った方には、まず最小限から始めたい）／よくあるご質問（権限を絞りすぎて、何も見えなくなりませんか）</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>§9 誤って塞ぐ</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>T-14.png</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
-      <c r="O26" s="8" t="inlineStr"/>
-      <c r="P26" s="8" t="inlineStr"/>
-      <c r="Q26" s="8" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="76" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>M2 制御が効く</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>作った権限どおりに画面が開く／開かない。直URLも塞がる</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>D. 制御が実際に効く</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>設定変更が反映される（即時または再ログイン）</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>設定変更後、対象ユーザーの次の画面遷移または再ログインで反映される。無反映＝0件（どちらの方式かは記録する）</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>権限を変更しても効かない</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>権限のキャッシュ・セッション</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>全画面（変更後に遷移）</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>T-08</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（設定した権限はいつから反映されますか）</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>§8-6</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>T-08.png</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="8" t="inlineStr"/>
-      <c r="P27" s="8" t="inlineStr"/>
-      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr"/>
+      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="R27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>既存の全管理者に権限が割り当たる（移行漏れ0）</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>ロール未割当=0名</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>権限が付いていない管理者はログインしても何も見えない</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>移行処理</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>ユーザー割当</t>
         </is>
       </c>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>T-18 T-21</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（権限が未設定の方はどうなりますか）</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>ユーザー割当一覧のスクショ（未割当0名）</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr"/>
-      <c r="O28" s="8" t="inlineStr"/>
-      <c r="P28" s="8" t="inlineStr"/>
-      <c r="Q28" s="8" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="76" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>AC-14</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1人1ロール。付け替えで前の権限が確実に外れる</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>割当編集で同時に選べる権限=1つ。付け替えで前の権限の画面=0件</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>前の権限が残り、想定外の画面が見えたままになる</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>割当編集／user_roles</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>割当編集</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>S-05 T-15</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる／担当店舗を設定する／権限を変更・解除する／権限をメンバーに割り当てる 方法1（すでに別の権限をお持ちの方）</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>§3.5 / §7-H 1人1ロール（2026-08-03・暫定）</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr"/>
-      <c r="O29" s="8" t="inlineStr"/>
-      <c r="P29" s="8" t="inlineStr"/>
-      <c r="Q29" s="8" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>付け替えで既存権限が置き換わることを事前に明示する</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>登録済み/置換予告が該当行に表示=100%</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>付け替えで意図せず権限を剥奪してしまう</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>割当編集／一括割当のUI</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>割当編集／一括割当</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>T-15 T-16</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる 方法1（対象は自動で絞り込まれます）／権限を変更・解除する／権限をメンバーに割り当てる 方法1（すでに別の権限をお持ちの方）</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>§5.4 事故防止3点</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>T-15.png</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
-      <c r="O30" s="8" t="inlineStr"/>
-      <c r="P30" s="8" t="inlineStr"/>
-      <c r="Q30" s="8" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="76" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>担当店舗を複数紐付けられる（人ごとに異なる範囲）</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>店長ベースで作った権限に2店舗を紐付けて保存できる</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>エリアマネージャーなど複数店舗を担当する権限が作れない</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>割当編集（store_ids）</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>割当編集（対象店舗）</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>S-05 T-11</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい ＋ 会社と店舗の両方の画面を使わせたい）／権限をメンバーに割り当てる／担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>§3.1④ / §7-B 担当店舗は割当側にのみ持たせる</t>
         </is>
       </c>
-      <c r="M31" s="8" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="8" t="inlineStr"/>
-      <c r="P31" s="8" t="inlineStr"/>
-      <c r="Q31" s="8" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="76" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>M3 人に配れる</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>権限を人に割り当て、担当店舗を紐付けられる</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>C. 権限を人に適用する</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>店舗ロールで担当店舗が未設定の割当を検知する</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>担当店舗0件のまま保存できない、または警告が出る。無警告のまま保存できる＝0件</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>担当店舗が未設定のまま割り当てられ、何も見えない人ができる</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>割当編集のバリデーション</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>割当編集</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する（権限を外す）／担当店舗を設定する（1つ以上お選びください）</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>§5.4</t>
         </is>
       </c>
-      <c r="M32" s="8" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>T-18.png</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="8" t="inlineStr"/>
-      <c r="P32" s="8" t="inlineStr"/>
-      <c r="Q32" s="8" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="76" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>master と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>適用前後で見える画面の増減=0</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>既存の master 権限で見える画面が増減する。増えれば情報漏洩、減れば業務停止</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>全画面（master でログイン）</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>—（現行からの移植。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>§4 段階導入</t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
-      <c r="O33" s="8" t="inlineStr"/>
-      <c r="P33" s="8" t="inlineStr"/>
-      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr"/>
+      <c r="Q33" s="4" t="inlineStr"/>
+      <c r="R33" s="4" t="inlineStr"/>
     </row>
     <row r="34" ht="76" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>manager と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>増減=0</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>既存の manager 権限で見える画面が増減する</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>全画面（manager でログイン）</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>—（現行からの移植。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr"/>
-      <c r="O34" s="8" t="inlineStr"/>
-      <c r="P34" s="8" t="inlineStr"/>
-      <c r="Q34" s="8" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="inlineStr"/>
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="76" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>M4 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>現行3権限と同じ動作のプリセットが用意され、移行漏れがない</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>E. 現行からの移植</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>shop_manager と同じ動作をするプリセットを用意する</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>増減=0</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>既存の shop_manager 権限で見える画面が増減する</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>移植プリセット</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>全画面（shop_manager でログイン）</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>S-06 T-21</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>—（現行からの移植。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>§4</t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>適用前後の全メニュー スクショ2枚</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr"/>
-      <c r="P35" s="8" t="inlineStr"/>
-      <c r="Q35" s="8" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr"/>
+      <c r="Q35" s="4" t="inlineStr"/>
+      <c r="R35" s="4" t="inlineStr"/>
     </row>
     <row r="36" ht="76" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>F. 事故を防ぐ</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>AC-17</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>自分の権限から権限設定を外せない（自己ロックアウト防止）</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>権限設定を自ロールから外す操作でブロックまたは警告が出る。無警告で保存できる＝0件</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>管理者が自分を締め出し、復旧に開発対応が必要になる</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>権限編集の保存時チェック</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>権限編集</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（自分の権限を変更できますか）</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>§9 自己ロックアウト</t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>T-17.png</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
-      <c r="O36" s="8" t="inlineStr"/>
-      <c r="P36" s="8" t="inlineStr"/>
-      <c r="Q36" s="8" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr"/>
+      <c r="Q36" s="4" t="inlineStr"/>
+      <c r="R36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="76" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>M5 事故らない</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>自分を締め出せない／一般権限で権限設定を触れない</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>F. 事故を防ぐ</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>一般の権限で権限設定ページを開けない</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>店舗ロールで権限設定URL=ブロック</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>一般の権限で権限設定を書き換えられる＝権限機能全体が無意味になる</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>権限設定画面の認可</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>権限設定（直URL）</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（自分の権限を変更できますか）</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>§9</t>
         </is>
       </c>
-      <c r="M37" s="8" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>T-17.png</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr"/>
-      <c r="O37" s="8" t="inlineStr"/>
-      <c r="P37" s="8" t="inlineStr"/>
-      <c r="Q37" s="8" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr"/>
+      <c r="Q37" s="4" t="inlineStr"/>
+      <c r="R37" s="4" t="inlineStr"/>
     </row>
     <row r="38" ht="76" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>一覧の許可数が実際の設定と一致する</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>不一致=0件（dataset/08 の**7権限すべて**）</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>一覧の表示と実際の設定がズレ、確認を誤る</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>権限一覧の集計</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="L38" s="8" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>設定内容を確認する（権限一覧）</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>§5.3 権限一覧</t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>T-05.png</t>
         </is>
       </c>
-      <c r="N38" s="8" t="inlineStr"/>
-      <c r="O38" s="8" t="inlineStr"/>
-      <c r="P38" s="8" t="inlineStr"/>
-      <c r="Q38" s="8" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="inlineStr"/>
+      <c r="R38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="76" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>権限編集はどの入口から入っても元の画面に戻る</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>4入口すべてで来た元に戻る（一覧/セルクリック/役割サマリ/割当編集）</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>修正のたびに元の場所へ辿り直すことになり、点検作業が重くなる</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>遷移の origin 保持</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>権限編集（4入口）</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する（入口の一覧表）</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>§5.6 F-06〜F-09</t>
         </is>
       </c>
-      <c r="M39" s="8" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>T-07.png</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
-      <c r="O39" s="8" t="inlineStr"/>
-      <c r="P39" s="8" t="inlineStr"/>
-      <c r="Q39" s="8" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr"/>
+      <c r="Q39" s="4" t="inlineStr"/>
+      <c r="R39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="76" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>役割サマリの割当人数が実態と一致する</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>**7権限すべてで** 表示N＝実保持者数（差分0）</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>割当人数の表示が実態とズレ、点検の判断を誤る</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>役割サマリの集計</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>役割サマリ</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>設定内容を確認する（役割サマリ）／権限をメンバーに割り当てる 方法3</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>§5.4 役割サマリ</t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>T-06.png</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr"/>
-      <c r="O40" s="8" t="inlineStr"/>
-      <c r="P40" s="8" t="inlineStr"/>
-      <c r="Q40" s="8" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr"/>
+      <c r="Q40" s="4" t="inlineStr"/>
+      <c r="R40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="76" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>H. 指標とオーナー</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>指標をまとめて設定でき、他の権限に再利用できる</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>テンプレ適用の結果が定義と一致。保存した組み合わせを他権限で読込できる</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>権限ごとに指標を作り直すことになり運用負荷が高い</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ（指標条件設定 ＋ マイテンプレート）／オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>§5.5</t>
         </is>
       </c>
-      <c r="M41" s="8" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>T-20.png</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr"/>
-      <c r="O41" s="8" t="inlineStr"/>
-      <c r="P41" s="8" t="inlineStr"/>
-      <c r="Q41" s="8" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr"/>
+      <c r="Q41" s="4" t="inlineStr"/>
+      <c r="R41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>H. 指標とオーナー</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>品質必須</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>オーナー専用機能が読取専用・オーナー限定である</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>指標管理に編集UI（トグル／コピー／条件設定）が表示される＝0件。オーナー以外が付与先指定を実行できる＝0件</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>全権の設定が誤って変更される</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>オーナー操作</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>オーナー操作</t>
         </is>
       </c>
-      <c r="K42" s="8" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="L42" s="8" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ（指標条件設定 ＋ マイテンプレート）／オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>§5.3 オーナー操作</t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>T-20.png</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="8" t="inlineStr"/>
-      <c r="P42" s="8" t="inlineStr"/>
-      <c r="Q42" s="8" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr"/>
+      <c r="Q42" s="4" t="inlineStr"/>
+      <c r="R42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="76" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>M6 運用できる</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>設定を点検でき、指標をまとめて設定できる</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>G. 設定を点検できる</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>AC-31</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>一覧の表示絞り込みが次回も保持される</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>画面を離れて戻ったとき、列選択が離脱前と一致（スコープ別に保持）</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>点検のたびに表示条件を選び直すことになる（利便性）</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>localStorage</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="K43" s="8" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>設定内容を確認する（権限一覧）</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>§5.3</t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>T-05.png</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr"/>
-      <c r="O43" s="8" t="inlineStr"/>
-      <c r="P43" s="8" t="inlineStr"/>
-      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr"/>
+      <c r="Q43" s="4" t="inlineStr"/>
+      <c r="R43" s="4" t="inlineStr"/>
     </row>
     <row r="44" ht="76" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>K-01</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>権限はロール経由でのみ付与する（人に直接付けない）</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>ユーザー個別に権限内容を編集できるUI・APIが存在しない＝0件</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>人ごとに権限を作り込めてしまい、従業員数だけ設定が増殖して誰が何を見えるか把握できなくなる</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>割当はロールの選択のみ。role_permissions はユーザーに紐付けない</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>ユーザー割当／割当編集</t>
         </is>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>—（設計の約束。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>§7-A 権限はロール経由で与える（人に直接付けない）</t>
         </is>
       </c>
-      <c r="M44" s="8" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr"/>
-      <c r="O44" s="8" t="inlineStr"/>
-      <c r="P44" s="8" t="inlineStr"/>
-      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr"/>
+      <c r="Q44" s="4" t="inlineStr"/>
+      <c r="R44" s="4" t="inlineStr"/>
     </row>
     <row r="45" ht="76" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>K-02</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>区分とデータ範囲を独立した軸として実装する</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>店舗ロールでも担当店舗を全店・複数店に設定できる＝**上限の制約がない**。※下限は AC-19 のとおり1件以上が必須（0件は保存不可）</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>「店舗ロール＝自店舗のみ」と固定され、エリアマネージャーや複数店舗所属が表現できない</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>user_roles.store_ids は区分と独立。区分でstore_idsを制限しない</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>割当編集（対象店舗）</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する（複数選択・全店）</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>§7-C 区分とデータ範囲は独立した別軸</t>
         </is>
       </c>
-      <c r="M45" s="8" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="8" t="inlineStr"/>
-      <c r="P45" s="8" t="inlineStr"/>
-      <c r="Q45" s="8" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr"/>
+      <c r="Q45" s="4" t="inlineStr"/>
+      <c r="R45" s="4" t="inlineStr"/>
     </row>
     <row r="46" ht="76" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>K-03</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>操作は登録・編集・削除を一体で扱う</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>権限の状態が なし／閲覧／操作 の3つ＝4つ目が存在しない</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>4状態に戻ると設定コストが跳ね上がり、顧客が使いこなせない</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>role_permissions.level は 0/1/2 のみ。削除専用フラグを作らない</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>権限編集（権限内容）</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L46" s="8" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 4（操作／閲覧／なし）</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>§7-D 操作＝登録・編集・削除を一体（削除を分けない） / §3.2</t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr"/>
-      <c r="O46" s="8" t="inlineStr"/>
-      <c r="P46" s="8" t="inlineStr"/>
-      <c r="Q46" s="8" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr"/>
+      <c r="Q46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="inlineStr"/>
     </row>
     <row r="47" ht="76" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>K-04</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>機密ランクを画面に出さない</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>指標一覧・指標条件設定に機密度のバッジ・ラベルが表示されない＝0件</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>顧客が指標を選ぶたびにランクの妥当性を判断させることになる</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>sens は初期値の算出にのみ使用。UIに描画しない</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>指標一覧／指標条件設定</t>
         </is>
       </c>
-      <c r="K47" s="8" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L47" s="8" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>—（設計の約束。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>§7-E 機密ランクを画面に出さない</t>
         </is>
       </c>
-      <c r="M47" s="8" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="8" t="inlineStr"/>
-      <c r="P47" s="8" t="inlineStr"/>
-      <c r="Q47" s="8" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr"/>
+      <c r="Q47" s="4" t="inlineStr"/>
+      <c r="R47" s="4" t="inlineStr"/>
     </row>
     <row r="48" ht="76" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>K-05</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>会社指標を店舗ロールに付与できる（禁止しない）</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>店舗ロールの指標一覧で会社指標をONにできる（ハードブロック＝0件）。初期状態のON件数は 従業員=会社0／店長=会社8</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>ハードブロックすると「店長にも全社利益を見せたい」という顧客の運用方針を否定する</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>既定OFF＋管理者オプトイン。行スコープ遮断とは独立</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>指標一覧（会社タブ）</t>
         </is>
       </c>
-      <c r="K48" s="8" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ（初期値は自動で設定されます）</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>§7-F 会社指標を店舗ロールに出すことを禁止しない</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr"/>
-      <c r="O48" s="8" t="inlineStr"/>
-      <c r="P48" s="8" t="inlineStr"/>
-      <c r="Q48" s="8" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr"/>
+      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="inlineStr"/>
     </row>
     <row r="49" ht="76" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>M7 境界設計が守られている</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>動作テストで見えない設計の約束が実装で守られている</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>K. 境界設計を守る（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>K-06</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>「含める」チェックを店舗選択と統合しない</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>一括割当で店舗を選んだだけでは権限が付与されない</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>誤クリックがそのまま権限付与になり、意図しない人に権限が渡る</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>含めるチェックを明示の安全装置として残す</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>一括割当</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="L49" s="8" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる 方法1</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>§7-G 「含める」チェックを店舗選択と統合しない</t>
         </is>
       </c>
-      <c r="M49" s="8" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>設計レビュー記録</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr"/>
-      <c r="O49" s="8" t="inlineStr"/>
-      <c r="P49" s="8" t="inlineStr"/>
-      <c r="Q49" s="8" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr"/>
+      <c r="Q49" s="4" t="inlineStr"/>
+      <c r="R49" s="4" t="inlineStr"/>
     </row>
     <row r="50" ht="76" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>M8 顧客価値に到達</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>顧客が求める権限（画面単位で表現できる範囲）が実際に作れる</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>I. 顧客価値に到達しているか</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>MVP必須</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>画面単位で表現できる4シナリオの権限が作れる</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>SC-01a経理（会社）／SC-01b経理（店舗）／SC-02人事／SC-04バイトL／SC-06スタッフ の5件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>顧客が求める権限を作れない＝リリースする意味がない</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>（総合判定）</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>全画面（6シナリオ）</t>
         </is>
       </c>
-      <c r="K50" s="8" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>T-22</t>
         </is>
       </c>
-      <c r="L50" s="8" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（6ケースすべて）</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>§1.2 顧客要望</t>
         </is>
       </c>
-      <c r="M50" s="8" t="inlineStr">
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>6シナリオの判定表</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr"/>
-      <c r="O50" s="8" t="inlineStr"/>
-      <c r="P50" s="8" t="inlineStr"/>
-      <c r="Q50" s="8" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr"/>
+      <c r="Q50" s="4" t="inlineStr"/>
+      <c r="R50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="76" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>担当外店舗のデータを返さない</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>他店データ=0件。2店舗合計=表示合計</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>担当外店舗のデータが混ざる。P3（データ範囲の強制）の要否判断に使う</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>P3 行スコープ強制</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>集計／売上分析</t>
         </is>
       </c>
-      <c r="K51" s="8" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>T-11 T-23</t>
         </is>
       </c>
-      <c r="L51" s="8" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する（今回のリリースでは、担当店舗は割り当ての記録として保存）</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>§3.1 ④ / §8-6</t>
         </is>
       </c>
-      <c r="M51" s="8" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>T-11.png</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr"/>
-      <c r="O51" s="8" t="inlineStr"/>
-      <c r="P51" s="8" t="inlineStr"/>
-      <c r="Q51" s="8" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr"/>
+      <c r="Q51" s="4" t="inlineStr"/>
+      <c r="R51" s="4" t="inlineStr"/>
     </row>
     <row r="52" ht="76" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>AC-24</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>閲覧のみの権限で更新できない</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>保存・登録・削除=不可（値が変わらない）</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>閲覧のみの権限で更新できてしまう。P2の要否判断に使う</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>P2 操作判定</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>費用設定／従業員管理</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="L52" s="8" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（画面は見せたいが、変更はさせたくない場合）</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>§3.1 ② / §8-6</t>
         </is>
       </c>
-      <c r="M52" s="8" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>T-23.png</t>
         </is>
       </c>
-      <c r="N52" s="8" t="inlineStr"/>
-      <c r="O52" s="8" t="inlineStr"/>
-      <c r="P52" s="8" t="inlineStr"/>
-      <c r="Q52" s="8" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr"/>
+      <c r="Q52" s="4" t="inlineStr"/>
+      <c r="R52" s="4" t="inlineStr"/>
     </row>
     <row r="53" ht="76" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>許可していない指標を表示しない</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>ダッシュボード・分析画面に非許可指標=0件</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>許可外の指標が表示される。P4の要否判断に使う</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>P4 指標可視性</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>ダッシュボード／分析画面</t>
         </is>
       </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>T-19 T-23</t>
         </is>
       </c>
-      <c r="L53" s="8" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ（今回のリリースでは、この設定は指標一覧の画面での選択状態を保存する）</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>§3.1 ③ / §5.5</t>
         </is>
       </c>
-      <c r="M53" s="8" t="inlineStr">
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>T-19.png</t>
         </is>
       </c>
-      <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="8" t="inlineStr"/>
-      <c r="P53" s="8" t="inlineStr"/>
-      <c r="Q53" s="8" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr"/>
+      <c r="P53" s="4" t="inlineStr"/>
+      <c r="Q53" s="4" t="inlineStr"/>
+      <c r="R53" s="4" t="inlineStr"/>
     </row>
     <row r="54" ht="76" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>AC-26</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>変更が監査ログに残る</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>権限の作成・割当の変更が操作ログに記録される＝記録漏れ0件（P1では実測を記録するのみ）</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>変更履歴が残らない。P5の要否判断に使う</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>P5 audit_logs</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>（管理画面のログ）</t>
         </is>
       </c>
-      <c r="K54" s="8" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>—（監査ログ。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>§6 audit_logs</t>
         </is>
       </c>
-      <c r="M54" s="8" t="inlineStr">
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>T-23.png</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr"/>
-      <c r="O54" s="8" t="inlineStr"/>
-      <c r="P54" s="8" t="inlineStr"/>
-      <c r="Q54" s="8" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr"/>
+      <c r="Q54" s="4" t="inlineStr"/>
+      <c r="R54" s="4" t="inlineStr"/>
     </row>
     <row r="55" ht="76" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>AC-32</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>データ範囲・操作を要する権限が作れる</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>**次段階の到達目標**。SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）。**P1では×が想定され、×であること自体が P2（操作制限）・P3（データ範囲）を前倒しする根拠になる**。P1では判定せず結果を記録する</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>データ範囲・操作を要する権限が作れない。P2/P3の前倒し判断に使う</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>P2／P3</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>全画面（SC-03／SC-05）</t>
         </is>
       </c>
-      <c r="K55" s="8" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>T-22 T-23</t>
         </is>
       </c>
-      <c r="L55" s="8" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（複数の店舗をまとめて見せたい）</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>§1.2 顧客要望 / §8-6</t>
         </is>
       </c>
-      <c r="M55" s="8" t="inlineStr">
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>T-22.png</t>
         </is>
       </c>
-      <c r="N55" s="8" t="inlineStr"/>
-      <c r="O55" s="8" t="inlineStr"/>
-      <c r="P55" s="8" t="inlineStr"/>
-      <c r="Q55" s="8" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr"/>
+      <c r="Q55" s="4" t="inlineStr"/>
+      <c r="R55" s="4" t="inlineStr"/>
     </row>
     <row r="56" ht="76" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>M9 次段階（P1対象外）</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>P1では実装しない。実測を記録し次の優先順位を決める</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>J. 次段階（P1では実装しない）</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>会社画面と店舗画面の両方を扱う権限が作れる</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>1人の権限で 会社画面（お支払い等）と店舗画面（費用設定等）の両方が開ける＝現状は×が想定</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>経理のように会社の支払と店舗の費用設定を両方見る職務が、1人1ロールでは表現できず権限を2つ作って人を分ける運用になる</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>user_roles（1人1ロール）／区分の設計</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>権限編集（区分）</t>
         </is>
       </c>
-      <c r="K56" s="8" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>T-09 T-09b</t>
         </is>
       </c>
-      <c r="L56" s="8" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（会社と店舗の両方の画面を使わせたい）</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>§3.5 / §7-C 区分とデータ範囲は独立した別軸</t>
         </is>
       </c>
-      <c r="M56" s="8" t="inlineStr">
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>T-09b.png</t>
         </is>
       </c>
-      <c r="N56" s="8" t="inlineStr"/>
-      <c r="O56" s="8" t="inlineStr"/>
-      <c r="P56" s="8" t="inlineStr"/>
-      <c r="Q56" s="8" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr"/>
+      <c r="P56" s="4" t="inlineStr"/>
+      <c r="Q56" s="4" t="inlineStr"/>
+      <c r="R56" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N17:N56">
+  <conditionalFormatting sqref="O17:O56">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3800,7 +4626,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N17:N56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O17:O56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>T-09〜T-14</t>
+          <t>T-09 T-09b T-10 T-11 T-12 T-13 T-14</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>T-09〜T-14</t>
+          <t>T-09 T-09b T-10 T-11 T-12 T-13 T-14</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>S-05 T-11</t>
+          <t>S-05 T-09b T-11</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -3306,7 +3306,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>作成した権限を修正する（入口の一覧表）</t>
+          <t>作成した権限を修正する（どこから入っても同じ編集画面）</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>担当店舗を設定する（複数選択・全店）</t>
+          <t>担当店舗を設定する（担当店舗は複数選択できます）</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1192,15 +1192,15 @@
       <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10">
-        <f>COUNTIF($A$17:$A$56,A5)</f>
+        <f>COUNTIF($A$17:$A$61,A5)</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS($A$17:$A$56,A5,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A5,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>COUNTIFS($A$17:$A$56,A5,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A5,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="10">
@@ -1226,15 +1226,15 @@
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10">
-        <f>COUNTIF($A$17:$A$56,A6)</f>
+        <f>COUNTIF($A$17:$A$61,A6)</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIFS($A$17:$A$56,A6,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A6,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>COUNTIFS($A$17:$A$56,A6,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A6,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="10">
@@ -1260,15 +1260,15 @@
       <c r="C7" s="10" t="inlineStr"/>
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="10">
-        <f>COUNTIF($A$17:$A$56,A7)</f>
+        <f>COUNTIF($A$17:$A$61,A7)</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS($A$17:$A$56,A7,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A7,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>COUNTIFS($A$17:$A$56,A7,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A7,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="10">
@@ -1294,15 +1294,15 @@
       <c r="C8" s="10" t="inlineStr"/>
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="10">
-        <f>COUNTIF($A$17:$A$56,A8)</f>
+        <f>COUNTIF($A$17:$A$61,A8)</f>
         <v/>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIFS($A$17:$A$56,A8,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A8,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>COUNTIFS($A$17:$A$56,A8,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A8,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="10">
@@ -1328,15 +1328,15 @@
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10">
-        <f>COUNTIF($A$17:$A$56,A9)</f>
+        <f>COUNTIF($A$17:$A$61,A9)</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS($A$17:$A$56,A9,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A9,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>COUNTIFS($A$17:$A$56,A9,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A9,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="10">
@@ -1362,15 +1362,15 @@
       <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="10" t="inlineStr"/>
       <c r="E10" s="10">
-        <f>COUNTIF($A$17:$A$56,A10)</f>
+        <f>COUNTIF($A$17:$A$61,A10)</f>
         <v/>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIFS($A$17:$A$56,A10,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A10,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>COUNTIFS($A$17:$A$56,A10,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A10,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="10">
@@ -1396,15 +1396,15 @@
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10">
-        <f>COUNTIF($A$17:$A$56,A11)</f>
+        <f>COUNTIF($A$17:$A$61,A11)</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS($A$17:$A$56,A11,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A11,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>COUNTIFS($A$17:$A$56,A11,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A11,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H11" s="10">
@@ -1430,15 +1430,15 @@
       <c r="C12" s="10" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="10">
-        <f>COUNTIF($A$17:$A$56,A12)</f>
+        <f>COUNTIF($A$17:$A$61,A12)</f>
         <v/>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIFS($A$17:$A$56,A12,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A12,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>COUNTIFS($A$17:$A$56,A12,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A12,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H12" s="10">
@@ -1464,15 +1464,15 @@
       <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="10">
-        <f>COUNTIF($A$17:$A$56,A13)</f>
+        <f>COUNTIF($A$17:$A$61,A13)</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS($A$17:$A$56,A13,$N$17:$N$56,"OK")</f>
+        <f>COUNTIFS($A$17:$A$61,A13,$N$17:$N$61,"OK")</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>COUNTIFS($A$17:$A$56,A13,$N$17:$N$56,"NG")</f>
+        <f>COUNTIFS($A$17:$A$61,A13,$N$17:$N$61,"NG")</f>
         <v/>
       </c>
       <c r="H13" s="10">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>T-18 T-21</t>
+          <t>T-18 T-21 T-25</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -4616,8 +4616,388 @@
       <c r="Q56" s="4" t="inlineStr"/>
       <c r="R56" s="4" t="inlineStr"/>
     </row>
+    <row r="57" ht="76" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>M5 事故らない</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>自分を締め出せない／一般権限で権限設定を触れない</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>F. 事故を防ぐ</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>AC-35</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>MVP必須</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>割当済みの権限は、割当を外すまで削除できない（警告を出す）</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>割当ユーザーが1名以上の権限で削除を実行→警告が出て削除されない＝100%。無警告で削除できる＝0件。割当0名なら削除できる</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>権限を消した瞬間にその人が未割当になり、ログインしても何も見えなくなる（業務停止）。AC-04（未割当0名）と衝突する</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧の削除ボタン／削除APIの事前チェック</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧（削除ボタン）</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>T-25</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する（権限を削除する）</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>§9 誤って壊す（2026-08-13 判断で追加）</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>T-25.png</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr"/>
+      <c r="Q57" s="4" t="inlineStr"/>
+      <c r="R57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="76" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>M3 人に配れる</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>権限を人に割り当て、担当店舗を紐付けられる</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>C. 権限を人に適用する</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>AC-36</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>MVP必須</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>「全店」は動的。店舗が増えたら自動的に対象に含まれる</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>「全店」の人がいる状態で店舗を1件追加→その人の対象店舗に自動で含まれる＝100%。再設定が必要＝0件</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>スナップショットだと新店舗が見えず業務が止まる。ただし動的にすると閲覧範囲が黙って広がるため、顧客への明示が必須</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗の解決ロジック（全店フラグ）</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>割当編集（対象店舗）／店舗管理</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>T-26</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する（担当店舗は複数選択できます）</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>§7 区分とデータ範囲は独立（2026-08-13 判断で追加）</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>T-26.png</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
+      <c r="Q58" s="4" t="inlineStr"/>
+      <c r="R58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="76" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>M3 人に配れる</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>権限を人に割り当て、担当店舗を紐付けられる</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>C. 権限を人に適用する</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>AC-37</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>品質必須</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>店舗の閉店・削除は不活性化。担当店舗の紐付けは保持する</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>店舗を閉店にしても担当店舗の紐付けが消えない＝100%。担当店舗が0件になる人＝0名</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗が0件になり AC-19（0件は保存不可）と矛盾する状態が生まれる。存在しない店舗IDが残る</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>店舗マスタの論理削除／担当店舗の解決ロジック</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>店舗管理／割当編集</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>T-26</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する（担当店舗は複数選択できます）</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>§7 区分とデータ範囲は独立（2026-08-13 判断で追加）</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>T-26.png</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr"/>
+      <c r="Q59" s="4" t="inlineStr"/>
+      <c r="R59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="76" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>M1 権限が作れる</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>顧客が自分で権限を作り、保存して再表示できる</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>B. 権限をつくる</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>AC-38</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>品質必須</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>権限名の重複を禁止し、別名を促すメッセージを出す</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>既存と同じ権限名で保存→エラーになり「別名で保存してください」が出る＝100%。重複したまま保存できる＝0件。別名に直せば保存できる</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>同じ名前の権限が並び、割当画面でどちらを選べばよいか判別できなくなる</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>権限保存時の一意チェック</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>権限編集（基本情報）</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>T-27</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>§5.2 基本情報（2026-08-13 判断で追加）</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>T-27.png</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr"/>
+      <c r="P60" s="4" t="inlineStr"/>
+      <c r="Q60" s="4" t="inlineStr"/>
+      <c r="R60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="76" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>M1 権限が作れる</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>顧客が自分で権限を作り、保存して再表示できる</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>B. 権限をつくる</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>AC-39</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>品質必須</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>区分を変えるときは既存権限を編集せず、新しい区分の権限として新規登録する</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>既存権限の区分は変更できない（プルダウンが編集時は固定）＝100%。区分を変えたい場合は新規作成に誘導される</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>区分を変えると設定対象の画面が入れ替わり、元の設定が意味を失う。何が残り何が消えたか誰にも分からなくなる</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>権限編集の基本情報（編集時は区分を非活性）</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>権限編集（基本情報）</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>T-27</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>§5.2 基本情報（2026-08-13 判断で追加）</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>T-27.png</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr"/>
+      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="R61" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="O17:O56">
+  <conditionalFormatting sqref="O17:O61">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4626,7 +5006,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O17:O56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O17:O61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1192,15 +1192,15 @@
       <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10">
-        <f>COUNTIF($A$17:$A$61,A5)</f>
+        <f>COUNTIF($A$17:$A$62,A5)</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS($A$17:$A$61,A5,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A5,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>COUNTIFS($A$17:$A$61,A5,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A5,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="10">
@@ -1226,15 +1226,15 @@
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10">
-        <f>COUNTIF($A$17:$A$61,A6)</f>
+        <f>COUNTIF($A$17:$A$62,A6)</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIFS($A$17:$A$61,A6,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A6,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>COUNTIFS($A$17:$A$61,A6,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A6,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="10">
@@ -1260,15 +1260,15 @@
       <c r="C7" s="10" t="inlineStr"/>
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="10">
-        <f>COUNTIF($A$17:$A$61,A7)</f>
+        <f>COUNTIF($A$17:$A$62,A7)</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS($A$17:$A$61,A7,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A7,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>COUNTIFS($A$17:$A$61,A7,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A7,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="10">
@@ -1294,15 +1294,15 @@
       <c r="C8" s="10" t="inlineStr"/>
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="10">
-        <f>COUNTIF($A$17:$A$61,A8)</f>
+        <f>COUNTIF($A$17:$A$62,A8)</f>
         <v/>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIFS($A$17:$A$61,A8,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A8,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>COUNTIFS($A$17:$A$61,A8,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A8,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="10">
@@ -1328,15 +1328,15 @@
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10">
-        <f>COUNTIF($A$17:$A$61,A9)</f>
+        <f>COUNTIF($A$17:$A$62,A9)</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS($A$17:$A$61,A9,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A9,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>COUNTIFS($A$17:$A$61,A9,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A9,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="10">
@@ -1362,15 +1362,15 @@
       <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="10" t="inlineStr"/>
       <c r="E10" s="10">
-        <f>COUNTIF($A$17:$A$61,A10)</f>
+        <f>COUNTIF($A$17:$A$62,A10)</f>
         <v/>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIFS($A$17:$A$61,A10,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A10,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>COUNTIFS($A$17:$A$61,A10,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A10,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="10">
@@ -1396,15 +1396,15 @@
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10">
-        <f>COUNTIF($A$17:$A$61,A11)</f>
+        <f>COUNTIF($A$17:$A$62,A11)</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS($A$17:$A$61,A11,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A11,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>COUNTIFS($A$17:$A$61,A11,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A11,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H11" s="10">
@@ -1430,15 +1430,15 @@
       <c r="C12" s="10" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="10">
-        <f>COUNTIF($A$17:$A$61,A12)</f>
+        <f>COUNTIF($A$17:$A$62,A12)</f>
         <v/>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIFS($A$17:$A$61,A12,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A12,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>COUNTIFS($A$17:$A$61,A12,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A12,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H12" s="10">
@@ -1464,15 +1464,15 @@
       <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="10">
-        <f>COUNTIF($A$17:$A$61,A13)</f>
+        <f>COUNTIF($A$17:$A$62,A13)</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS($A$17:$A$61,A13,$N$17:$N$61,"OK")</f>
+        <f>COUNTIFS($A$17:$A$62,A13,$N$17:$N$62,"OK")</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>COUNTIFS($A$17:$A$61,A13,$N$17:$N$61,"NG")</f>
+        <f>COUNTIFS($A$17:$A$62,A13,$N$17:$N$62,"NG")</f>
         <v/>
       </c>
       <c r="H13" s="10">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-07 T-27</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -4996,8 +4996,84 @@
       <c r="Q61" s="4" t="inlineStr"/>
       <c r="R61" s="4" t="inlineStr"/>
     </row>
+    <row r="62" ht="76" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>M1 権限が作れる</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>顧客が自分で権限を作り、保存して再表示できる</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>B. 権限をつくる</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>AC-40</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>MVP必須</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>既存権限の名前を変えて保存するとき、上書きか新規かを選ばせる</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>名前を変えて保存→選択が出る＝100%。「上書き」で権限数が増えない＝増加0件かつ保持者が新しい名前の権限を持つ。「新しい権限として保存」で元の権限が残り1件増える。名前を変えずに保存→選択は出ない</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>名前を直したつもりが元の権限ごと変わり、その権限を持つ全員に影響する。派生の権限を作りたかった顧客が、元の権限を失う</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>権限編集の保存時（名前の変更を検知して分岐）</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>権限編集（基本情報）</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>T-07 T-27</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する（どこから入っても同じ編集画面）</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>§5.2 権限編集（2026-08-14 判断で追加）</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>T-27.png</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
+      <c r="Q62" s="4" t="inlineStr"/>
+      <c r="R62" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="O17:O61">
+  <conditionalFormatting sqref="O17:O62">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5006,7 +5082,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O17:O61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O17:O62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_01_受入条件表.xlsx
+++ b/20260804_権限設定_01_受入条件表.xlsx
@@ -1832,17 +1832,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>雛形（ベース）から差分で作れる。移植プリセットを候補に出す</t>
+          <t>雛形（ベース）から差分で作れる。候補を スタンダード／カスタマイズ／新規作成 の3つに分ける</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>ベース選択に4種（オーナー相当/本部管理/店長/従業員）＋**まっさら（なし）**が出る。エリア長は含まれない</t>
+          <t>ベース選択が3つの大カテゴリに分かれる。スタンダードテンプレ＝4種（全権オーナー相当/本部管理/店長/従業員）、カスタマイズテンプレ＝顧客が作った権限、新規作成＝1件。エリア長はスタンダードに含まれない</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27画面をゼロから設定することになり、実運用が回らない</t>
+          <t>27画面をゼロから設定することになる。また既定と自社作成の区別がつかず、どれを土台にすべきか判断できない</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
